--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -569,7 +569,7 @@
         <v>43345</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         <v>44826</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44872</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44575</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>44575</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44088</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44484</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44974</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>44340</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44743</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44958</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45201</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>43315</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45196</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>45208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45301</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>43320</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>43353</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>43474</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43475</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43523</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>43524</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>43531</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43585</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43807</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>43809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>43879</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>43990</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44092</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44235</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44342</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44435</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44608</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44636</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44642</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44690</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44706</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44754</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44801</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44914</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44960</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44974</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45007</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45049</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45093</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45093</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45093</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45093</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45216</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45294</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>43320</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>43321</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>43321</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>43325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>43328</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>43335</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>43336</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>43336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>43340</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>43341</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>43346</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>43348</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>43355</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>43356</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>43356</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>43357</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>43368</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>43375</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>43376</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>43383</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>43385</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>43388</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>43395</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>43395</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>43402</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>43402</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>43402</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>43402</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>43406</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>43411</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>43412</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>43414</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43423</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43423</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>43426</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43440</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43441</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43441</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>43441</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>43441</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43441</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>43445</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>43445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>43445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>43446</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>43454</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>43454</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43467</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43467</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43468</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43473</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43474</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43475</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>43475</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>43481</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>43481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>43482</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>43487</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>43487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>43487</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>43488</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>43493</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43494</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43496</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43501</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43506</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43508</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43511</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43514</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>43515</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>43517</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>43528</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43528</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43530</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43533</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43542</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43542</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43543</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>43558</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43563</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43573</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43578</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43579</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43579</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43580</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43584</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>43584</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>43584</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>43588</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>43589</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>43593</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>43594</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>43595</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>43599</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>43600</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>43602</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>43608</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>43612</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>43612</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43612</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>43619</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>43619</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>43621</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>43621</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>43626</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>43626</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>43634</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>43634</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>43636</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>43644</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>43647</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>43647</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>43649</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>43649</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>43651</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>43657</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>43657</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>43657</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>43661</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>43672</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>43679</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>43682</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>43683</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>43689</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43689</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43691</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>43698</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>43698</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>43699</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>43702</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>43703</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43711</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>43712</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43714</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43719</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43721</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>43725</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>43727</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>43727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>43727</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>43731</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>43740</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>43742</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>43748</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43748</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43756</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43762</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43765</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43766</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43767</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43773</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43773</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43773</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43775</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43781</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>43782</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43782</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43783</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43787</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>43795</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>43795</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>43796</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>43796</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>43796</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>43803</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>43809</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>43811</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>43850</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>43852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>43858</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>43858</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>43858</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>43858</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>43860</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43860</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43860</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>43860</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>43865</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>43866</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>43868</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>43868</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>43868</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43868</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43871</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43871</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43871</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43871</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43871</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43871</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43879</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>43882</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>43885</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>43886</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>43892</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43893</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>43893</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>43910</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>43914</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>43917</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>43924</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>43930</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>43936</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>43936</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>43936</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>43937</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>43938</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>43941</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>43956</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>43956</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>43956</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>43956</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>43956</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>43957</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>43957</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>43976</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>43977</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>43977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>43980</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>43980</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>43980</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>43990</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44000</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44007</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44008</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>44011</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44026</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44029</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44034</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44039</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44039</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44047</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44049</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44050</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44053</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44057</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44063</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44063</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44063</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44067</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44068</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>44069</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44069</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44076</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>44077</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44078</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44084</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44084</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44088</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44089</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44090</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44092</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44095</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>44099</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44100</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44104</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>44105</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44112</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>44112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>44112</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44112</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44112</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>44113</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44120</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44123</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44123</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44124</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>44125</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44130</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44140</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>44144</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44148</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44160</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44161</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44164</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44165</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44167</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44168</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44168</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44171</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44171</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44172</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>44187</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>44203</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>44203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>44203</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44207</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44215</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>44216</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44218</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>44218</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>44221</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44223</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44223</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44236</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44239</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44242</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44243</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44244</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44249</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44249</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44252</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44258</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>44266</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>44266</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44267</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>44272</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>44274</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>44278</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44284</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>44284</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>44294</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>44294</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>44308</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44309</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>44309</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>44313</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44314</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>44316</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>44319</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>44319</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>44319</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>44320</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>44322</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>44323</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>44326</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>44334</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>44334</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44335</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44337</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44337</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>44341</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>44354</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44357</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44361</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44375</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44375</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>44379</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44379</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44379</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44379</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44379</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44382</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>44383</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>44392</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>44411</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>44411</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>44416</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44418</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>44419</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>44425</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>44425</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>44425</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>44433</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>44434</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44435</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44439</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>44442</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>44445</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44447</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>44452</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>44452</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>44454</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>44454</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44454</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>44454</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44455</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>44456</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>44460</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44462</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44463</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44465</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44466</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44466</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44466</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44466</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44467</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44469</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44469</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44480</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44483</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44483</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>44483</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>44483</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>44483</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44484</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>44484</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44484</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44486</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>44487</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>44497</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>44500</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>44501</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>44502</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>44505</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>44516</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>44517</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>44517</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>44525</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>44539</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>44558</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44560</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>44567</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>44567</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>44568</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44575</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44578</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>44585</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>44587</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44587</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>44587</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>44587</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>44589</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>44594</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44596</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>44599</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>44600</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>44603</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>44606</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44608</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44608</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>44616</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>44616</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>44617</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>44623</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>44627</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44645</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>44650</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>44655</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>44657</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>44658</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>44677</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>44677</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>44687</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>44697</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>44699</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>44699</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>44699</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>44701</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>44704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>44714</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>44720</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>44725</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44728</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>44728</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44729</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44733</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44734</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44734</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44739</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>44739</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44739</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>44742</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>44743</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>44755</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>44776</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>44782</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>44782</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>44789</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>44795</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>44796</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44799</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44799</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44799</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44799</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44799</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44801</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44801</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44804</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44805</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44805</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>44805</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>44805</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44805</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44811</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44826</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>44830</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>44836</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44837</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44839</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>44846</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>44851</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>44852</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>44852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44854</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>44860</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44861</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44865</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>44868</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>44873</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44873</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>44874</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>44882</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>44882</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>44882</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>44882</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>44882</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>44886</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>44886</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>44886</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>44889</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44889</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>44890</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>44894</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44897</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>44897</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44907</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>44908</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>44918</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>44918</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>44918</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>44918</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44918</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>44918</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>44918</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44918</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>44918</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>44918</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>44918</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>44923</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>44924</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>44925</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>44930</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>44935</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>44935</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>44937</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>44937</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44939</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>44944</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>44949</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44949</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44949</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>44949</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44951</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>44952</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>44952</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44952</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>44952</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>44952</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44952</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>44952</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>44952</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>44953</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>44953</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>44956</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>44956</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>44958</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>44958</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>44958</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44959</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>44959</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>44960</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>44960</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>44963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44964</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44965</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>44967</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>44970</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>44974</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44974</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>44974</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>44977</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>44977</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>44977</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>44977</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>44978</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>44978</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>44978</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>44978</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>44981</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>44981</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44982</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>44982</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>44982</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>44984</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>44988</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44991</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>44991</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>44992</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>44992</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>44992</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44992</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>44993</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45000</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45000</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>45000</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45000</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45000</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45001</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45005</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>45005</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45007</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45007</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45007</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45007</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45008</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45009</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>45009</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45014</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45020</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45020</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45020</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45020</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45020</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45029</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45030</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45030</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45030</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45030</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45035</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>45035</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>45036</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45036</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45044</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45048</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45056</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45057</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45062</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45062</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45062</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45062</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45062</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45063</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45071</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45071</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45071</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>45076</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>45077</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45078</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45078</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45078</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45078</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45078</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45078</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45078</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45078</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45078</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45078</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45078</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45078</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45078</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45078</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45082</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45082</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45082</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45082</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45082</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45084</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>45085</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45086</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>45089</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45091</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>45091</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45091</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45093</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45093</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45096</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45096</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45097</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45097</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>45097</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>45098</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45098</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45098</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>45098</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>45098</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>45105</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48992,7 +48992,7 @@
         <v>45107</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49049,7 +49049,7 @@
         <v>45107</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45110</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>45111</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>45111</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>45111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45112</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45114</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45116</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45118</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45118</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45120</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45122</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45123</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45123</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45128</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45134</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45139</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45139</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45141</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45145</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45145</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45145</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45145</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45145</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45145</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45145</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45145</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45147</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45148</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45149</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45151</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45154</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45154</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>45159</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45160</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45160</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>45160</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45161</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45161</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45161</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>45162</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45163</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45163</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45163</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45163</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45166</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45166</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45166</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45167</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45168</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45169</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45171</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52618,7 +52618,7 @@
         <v>45174</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45174</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45174</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45174</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>45175</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>45175</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52960,7 +52960,7 @@
         <v>45176</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>45176</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>45176</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>45181</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>45182</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>45183</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>45184</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>45184</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>45187</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>45187</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45187</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45187</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45187</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45187</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45187</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45188</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45188</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45188</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45191</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>45194</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>45194</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45194</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45195</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         <v>45195</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         <v>45196</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45196</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45197</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45197</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45198</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54737,7 +54737,7 @@
         <v>45200</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
         <v>45199</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>45201</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45201</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>45201</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>45201</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55079,7 +55079,7 @@
         <v>45201</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55136,7 +55136,7 @@
         <v>45202</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         <v>45202</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         <v>45202</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45204</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>45209</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45210</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45211</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45215</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55597,7 +55597,7 @@
         <v>45216</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>45216</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45219</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45219</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45219</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45219</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45219</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>45222</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56053,7 +56053,7 @@
         <v>45222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45223</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45224</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56338,7 +56338,7 @@
         <v>45226</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56395,7 +56395,7 @@
         <v>45226</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>45226</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>45229</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45229</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56623,7 +56623,7 @@
         <v>45229</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45229</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45229</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45229</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45229</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56923,7 +56923,7 @@
         <v>45230</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56980,7 +56980,7 @@
         <v>45232</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57037,7 +57037,7 @@
         <v>45232</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45232</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57151,7 +57151,7 @@
         <v>45232</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>45232</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45232</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>45232</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>45232</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57436,7 +57436,7 @@
         <v>45235</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45235</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>45238</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>45240</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57664,7 +57664,7 @@
         <v>45240</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57835,7 +57835,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45245</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45245</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45245</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58120,7 +58120,7 @@
         <v>45246</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45246</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45246</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45246</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45247</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45247</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45250</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45250</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45250</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45254</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45257</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45257</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45257</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45259</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45260</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45260</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45260</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45260</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45260</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45260</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>45260</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59545,7 +59545,7 @@
         <v>45261</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59602,7 +59602,7 @@
         <v>45264</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59659,7 +59659,7 @@
         <v>45264</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45265</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45267</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45274</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45275</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60410,7 +60410,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60472,7 +60472,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45279</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60700,7 +60700,7 @@
         <v>45279</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>45279</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>45279</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60871,7 +60871,7 @@
         <v>45281</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60928,7 +60928,7 @@
         <v>45281</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>45290</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61042,7 +61042,7 @@
         <v>45294</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61099,7 +61099,7 @@
         <v>45299</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45301</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>45301</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61270,7 +61270,7 @@
         <v>45301</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45301</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61384,7 +61384,7 @@
         <v>45302</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45302</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>45303</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>45308</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61726,7 +61726,7 @@
         <v>45308</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         <v>45308</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61840,7 +61840,7 @@
         <v>45308</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61897,7 +61897,7 @@
         <v>45308</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>45314</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62061,14 +62061,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 2755-2024</t>
+          <t>A 2758-2024</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>6.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -62118,14 +62118,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 2759-2024</t>
+          <t>A 2755-2024</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62138,7 +62138,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -62175,14 +62175,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 2758-2024</t>
+          <t>A 2759-2024</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>9.699999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -62239,7 +62239,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62296,7 +62296,7 @@
         <v>45315</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62346,14 +62346,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 2966-2024</t>
+          <t>A 2969-2024</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62366,7 +62366,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -62403,14 +62403,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 2967-2024</t>
+          <t>A 2966-2024</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62423,7 +62423,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -62467,7 +62467,7 @@
         <v>45315</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62517,14 +62517,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 2969-2024</t>
+          <t>A 2952-2024</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -62574,14 +62574,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 2952-2024</t>
+          <t>A 2967-2024</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -62631,14 +62631,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 3378-2024</t>
+          <t>A 3379-2024</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62651,7 +62651,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -62688,14 +62688,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 3379-2024</t>
+          <t>A 3380-2024</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62708,7 +62708,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -62745,14 +62745,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 3380-2024</t>
+          <t>A 3378-2024</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62765,7 +62765,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -62809,7 +62809,7 @@
         <v>45320</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62859,14 +62859,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 3820-2024</t>
+          <t>A 3761-2024</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62879,7 +62879,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -62916,14 +62916,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 3823-2024</t>
+          <t>A 3765-2024</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62936,7 +62936,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>4.9</v>
+        <v>10.2</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -62973,14 +62973,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 3761-2024</t>
+          <t>A 3820-2024</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62993,7 +62993,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -63030,14 +63030,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 3765-2024</t>
+          <t>A 3823-2024</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63050,7 +63050,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>10.2</v>
+        <v>4.9</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -63094,7 +63094,7 @@
         <v>45323</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63151,7 +63151,7 @@
         <v>45324</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63208,7 +63208,7 @@
         <v>45327</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63265,7 +63265,7 @@
         <v>45327</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63379,7 +63379,7 @@
         <v>45330</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>45331</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>45331</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63550,7 +63550,7 @@
         <v>45333</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63607,7 +63607,7 @@
         <v>45334</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63664,7 +63664,7 @@
         <v>45334</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63721,7 +63721,7 @@
         <v>45337</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45337</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -569,7 +569,7 @@
         <v>43345</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         <v>44826</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44872</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44575</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>44575</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44088</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44484</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44974</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>44340</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44743</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44958</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45201</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>43315</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45196</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>45208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45301</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>43320</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>43353</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>43474</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43475</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43523</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>43524</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>43531</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43585</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43807</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>43809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>43879</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>43990</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44092</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44235</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44342</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44435</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44608</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44636</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44642</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44690</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44706</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44754</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44801</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44914</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44960</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44974</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45007</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45049</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45093</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45093</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45093</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45093</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45216</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45294</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>43320</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>43321</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>43321</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>43325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>43328</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>43335</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>43336</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>43336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>43340</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>43341</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>43346</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>43348</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>43355</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>43356</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>43356</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>43357</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>43368</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>43375</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>43376</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>43383</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>43385</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>43388</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>43395</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>43395</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>43402</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>43402</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>43402</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>43402</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>43406</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>43411</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>43412</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>43414</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43423</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43423</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>43426</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43440</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43441</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43441</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>43441</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>43441</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43441</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>43445</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>43445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>43445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>43446</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>43454</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>43454</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43467</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43467</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43468</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43473</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43474</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43475</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>43475</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>43481</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>43481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>43482</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>43487</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>43487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>43487</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>43488</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>43493</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43494</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43496</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43501</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43506</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43508</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43511</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43514</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>43515</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>43517</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>43528</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43528</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43530</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43533</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43542</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43542</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43543</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>43558</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43563</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43573</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43578</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43579</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43579</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43580</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43584</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>43584</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>43584</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>43588</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>43589</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>43593</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>43594</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>43595</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>43599</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>43600</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>43602</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>43608</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>43612</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>43612</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43612</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>43619</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>43619</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>43621</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>43621</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>43626</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>43626</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>43634</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>43634</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>43636</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>43644</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>43647</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>43647</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>43649</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>43649</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>43651</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>43657</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>43657</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>43657</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>43661</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>43672</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>43679</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>43682</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>43683</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>43689</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43689</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43691</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>43698</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>43698</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>43699</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>43702</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>43703</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43711</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>43712</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43714</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43719</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43721</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>43725</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>43727</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>43727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>43727</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>43731</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>43740</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>43742</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>43748</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43748</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43756</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43762</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43765</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43766</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43767</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43773</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43773</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43773</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43775</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43781</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>43782</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43782</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43783</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43787</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>43795</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>43795</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>43796</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>43796</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>43796</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>43803</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>43809</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>43811</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>43850</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>43852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>43858</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>43858</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>43858</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>43858</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>43860</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43860</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43860</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>43860</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>43865</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>43866</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>43868</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>43868</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>43868</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43868</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43871</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43871</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43871</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43871</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43871</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43871</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43879</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>43882</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>43885</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>43886</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>43892</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43893</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>43893</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>43910</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>43914</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>43917</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>43924</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>43930</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>43936</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>43936</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>43936</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>43937</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>43938</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>43941</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>43956</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>43956</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>43956</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>43956</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>43956</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>43957</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>43957</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>43976</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>43977</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>43977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>43980</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>43980</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>43980</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>43990</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44000</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44007</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44008</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>44011</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44026</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44029</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44034</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44039</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44039</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44047</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44049</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44050</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44053</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44057</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44063</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44063</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44063</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44067</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44068</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>44069</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44069</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44076</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>44077</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44078</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44084</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44084</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44088</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44089</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44090</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44092</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44095</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>44099</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44100</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44104</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>44105</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44112</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>44112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>44112</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44112</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44112</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>44113</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44120</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44123</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44123</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44124</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>44125</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44130</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44140</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>44144</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44148</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44160</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44161</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44164</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44165</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44167</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44168</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44168</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44171</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44171</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44172</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>44187</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>44203</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>44203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>44203</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44207</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44215</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>44216</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44218</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>44218</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>44221</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44223</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44223</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44236</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44239</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44242</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44243</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44244</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44249</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44249</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44252</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44258</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>44266</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>44266</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44267</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>44272</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>44274</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>44278</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44284</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>44284</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>44294</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>44294</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>44308</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44309</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>44309</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>44313</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44314</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>44316</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>44319</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>44319</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>44319</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>44320</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>44322</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>44323</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>44326</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>44334</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>44334</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44335</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44337</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44337</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>44341</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>44354</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44357</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44361</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44375</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44375</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>44379</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44379</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44379</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44379</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44379</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44382</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>44383</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>44392</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>44411</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>44411</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>44416</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44418</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>44419</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>44425</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>44425</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>44425</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>44433</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>44434</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44435</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44439</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>44442</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>44445</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44447</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>44452</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>44452</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>44454</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>44454</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44454</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>44454</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44455</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>44456</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>44460</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44462</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44463</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44465</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44466</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44466</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44466</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44466</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44467</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44469</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44469</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44480</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44483</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44483</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>44483</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>44483</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>44483</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44484</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>44484</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44484</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44486</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>44487</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>44497</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>44500</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>44501</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>44502</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>44505</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>44516</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>44517</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>44517</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>44525</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>44539</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>44558</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44560</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>44567</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>44567</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>44568</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44575</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44578</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>44585</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>44587</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44587</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>44587</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>44587</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>44589</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>44594</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44596</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>44599</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>44600</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>44603</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>44606</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44608</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44608</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>44616</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>44616</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>44617</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>44623</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>44627</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44645</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>44650</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>44655</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>44657</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>44658</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>44677</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>44677</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>44687</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>44697</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>44699</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>44699</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>44699</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>44701</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>44704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>44714</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>44720</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>44725</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44728</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>44728</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44729</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44733</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44734</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44734</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44739</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>44739</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44739</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>44742</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>44743</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>44755</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>44776</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>44782</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>44782</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>44789</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>44795</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>44796</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44799</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44799</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44799</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44799</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44799</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44801</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44801</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44804</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44805</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44805</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>44805</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>44805</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44805</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44811</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44826</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>44830</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>44836</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44837</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44839</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>44846</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>44851</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>44852</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>44852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44854</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>44860</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44861</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44865</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>44868</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>44873</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44873</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>44874</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>44882</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>44882</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>44882</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>44882</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>44882</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>44886</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>44886</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>44886</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>44889</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44889</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>44890</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>44894</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44897</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>44897</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44907</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>44908</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>44918</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>44918</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>44918</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>44918</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44918</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>44918</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>44918</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44918</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>44918</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>44918</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>44918</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>44923</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>44924</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>44925</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>44930</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>44935</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>44935</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>44937</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>44937</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44939</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>44944</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>44949</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44949</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44949</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>44949</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44951</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>44952</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>44952</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44952</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>44952</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>44952</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44952</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>44952</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>44952</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>44953</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>44953</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>44956</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>44956</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>44958</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>44958</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>44958</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44959</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>44959</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>44960</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>44960</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>44963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44964</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44965</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>44967</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>44970</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>44974</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44974</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>44974</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>44977</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>44977</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>44977</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>44977</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>44978</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>44978</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>44978</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>44978</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>44981</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>44981</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44982</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>44982</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>44982</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>44984</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>44988</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44991</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>44991</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>44992</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>44992</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>44992</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44992</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>44993</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45000</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45000</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>45000</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45000</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45000</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45001</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45005</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>45005</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45007</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45007</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45007</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45007</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45008</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45009</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>45009</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45014</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45020</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45020</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45020</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45020</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45020</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45029</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45030</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45030</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45030</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45030</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45035</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>45035</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>45036</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45036</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45044</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45048</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45056</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45057</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45062</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45062</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45062</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45062</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45062</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45063</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45071</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45071</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45071</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>45076</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>45077</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45078</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45078</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45078</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45078</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45078</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45078</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45078</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45078</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45078</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45078</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45078</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45078</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45078</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45078</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45082</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45082</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45082</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45082</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45082</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45084</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>45085</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45086</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>45089</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45091</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>45091</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45091</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45093</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45093</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45096</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45096</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45097</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45097</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>45097</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>45098</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45098</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45098</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>45098</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>45098</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>45105</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48992,7 +48992,7 @@
         <v>45107</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49049,7 +49049,7 @@
         <v>45107</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45110</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>45111</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>45111</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>45111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45112</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45114</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45116</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45118</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45118</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45120</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45122</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45123</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45123</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45128</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45134</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45139</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45139</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45141</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45145</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45145</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45145</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45145</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45145</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45145</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45145</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45145</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45147</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45148</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45149</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45151</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45154</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45154</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>45159</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45160</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45160</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>45160</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45161</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45161</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45161</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>45162</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45163</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45163</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45163</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45163</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45166</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45166</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45166</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45167</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45168</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45169</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45171</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52618,7 +52618,7 @@
         <v>45174</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45174</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45174</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45174</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>45175</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>45175</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52960,7 +52960,7 @@
         <v>45176</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>45176</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>45176</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>45181</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>45182</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>45183</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>45184</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>45184</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>45187</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>45187</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45187</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45187</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45187</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45187</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45187</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45188</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45188</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45188</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45191</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>45194</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>45194</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45194</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45195</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         <v>45195</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         <v>45196</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45196</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45197</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45197</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45198</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54737,7 +54737,7 @@
         <v>45200</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
         <v>45199</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>45201</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45201</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>45201</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>45201</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55079,7 +55079,7 @@
         <v>45201</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55136,7 +55136,7 @@
         <v>45202</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         <v>45202</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         <v>45202</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45204</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>45209</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45210</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45211</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45215</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55597,7 +55597,7 @@
         <v>45216</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>45216</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45219</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45219</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45219</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45219</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45219</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>45222</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56053,7 +56053,7 @@
         <v>45222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45223</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45224</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56338,7 +56338,7 @@
         <v>45226</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56395,7 +56395,7 @@
         <v>45226</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>45226</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>45229</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45229</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56623,7 +56623,7 @@
         <v>45229</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45229</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45229</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45229</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45229</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56923,7 +56923,7 @@
         <v>45230</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56980,7 +56980,7 @@
         <v>45232</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57037,7 +57037,7 @@
         <v>45232</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45232</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57151,7 +57151,7 @@
         <v>45232</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>45232</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45232</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>45232</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>45232</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57436,7 +57436,7 @@
         <v>45235</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45235</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>45238</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>45240</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57664,7 +57664,7 @@
         <v>45240</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57835,7 +57835,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45245</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45245</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45245</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58120,7 +58120,7 @@
         <v>45246</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45246</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45246</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45246</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45247</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45247</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45250</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45250</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45250</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45254</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45257</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45257</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45257</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45259</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45260</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45260</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45260</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45260</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45260</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45260</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>45260</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59545,7 +59545,7 @@
         <v>45261</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59602,7 +59602,7 @@
         <v>45264</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59659,7 +59659,7 @@
         <v>45264</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45265</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45267</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45274</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45275</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60410,7 +60410,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60472,7 +60472,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45279</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60700,7 +60700,7 @@
         <v>45279</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>45279</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>45279</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60871,7 +60871,7 @@
         <v>45281</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60928,7 +60928,7 @@
         <v>45281</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>45290</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61042,7 +61042,7 @@
         <v>45294</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61099,7 +61099,7 @@
         <v>45299</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45301</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>45301</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61270,7 +61270,7 @@
         <v>45301</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45301</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61384,7 +61384,7 @@
         <v>45302</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45302</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>45303</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>45308</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61726,7 +61726,7 @@
         <v>45308</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         <v>45308</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61840,7 +61840,7 @@
         <v>45308</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61897,7 +61897,7 @@
         <v>45308</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62004,14 +62004,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 2755-2024</t>
+          <t>A 2638-2024</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62024,7 +62024,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -62061,14 +62061,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 2759-2024</t>
+          <t>A 2755-2024</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -62118,14 +62118,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 2765-2024</t>
+          <t>A 2759-2024</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62138,7 +62138,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -62175,14 +62175,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 2638-2024</t>
+          <t>A 2758-2024</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -62232,14 +62232,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 2758-2024</t>
+          <t>A 2765-2024</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62252,7 +62252,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>9.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -62296,7 +62296,7 @@
         <v>45315</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62346,14 +62346,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 2966-2024</t>
+          <t>A 2957-2024</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62366,7 +62366,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -62403,14 +62403,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 2897-2024</t>
+          <t>A 2969-2024</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62423,7 +62423,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -62460,14 +62460,14 @@
     <row r="1048" ht="15" customHeight="1">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>A 2952-2024</t>
+          <t>A 2897-2024</t>
         </is>
       </c>
       <c r="B1048" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62480,7 +62480,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -62517,14 +62517,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 2957-2024</t>
+          <t>A 2966-2024</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -62574,14 +62574,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 2969-2024</t>
+          <t>A 2952-2024</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -62631,14 +62631,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 3380-2024</t>
+          <t>A 3379-2024</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62651,7 +62651,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -62688,14 +62688,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 3378-2024</t>
+          <t>A 3380-2024</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62708,7 +62708,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -62745,14 +62745,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 3379-2024</t>
+          <t>A 3378-2024</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62765,7 +62765,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -62809,7 +62809,7 @@
         <v>45320</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62866,7 +62866,7 @@
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63037,7 +63037,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63094,7 +63094,7 @@
         <v>45323</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63151,7 +63151,7 @@
         <v>45324</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63208,7 +63208,7 @@
         <v>45327</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63265,7 +63265,7 @@
         <v>45327</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63379,7 +63379,7 @@
         <v>45330</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>45331</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>45331</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63550,7 +63550,7 @@
         <v>45333</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63600,14 +63600,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5706-2024</t>
+          <t>A 5707-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -63657,14 +63657,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5707-2024</t>
+          <t>A 5706-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -63721,7 +63721,7 @@
         <v>45337</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45337</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45341</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45341</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45341</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -569,7 +569,7 @@
         <v>43345</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         <v>44826</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44872</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44575</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>44575</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44088</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44484</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44974</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>44340</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44743</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44958</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45201</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>43315</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45196</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>45208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45301</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>43320</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>43353</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>43474</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43475</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43523</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>43524</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>43531</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43585</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43807</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>43809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>43879</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>43990</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44092</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44235</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44342</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44435</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44608</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44636</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44642</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44690</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44706</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44754</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44801</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44914</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44960</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44974</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45007</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45049</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45093</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45093</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45093</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45093</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45216</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45294</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>43320</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>43321</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>43321</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>43325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>43328</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>43335</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>43336</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>43336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>43340</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>43341</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>43346</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>43348</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>43355</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>43356</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>43356</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>43357</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>43368</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>43375</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>43376</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>43383</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>43385</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>43388</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>43395</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>43395</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>43402</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>43402</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>43402</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>43402</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>43406</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>43411</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>43412</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>43414</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43423</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43423</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>43426</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43440</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43441</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43441</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>43441</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>43441</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43441</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>43445</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>43445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>43445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>43446</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>43454</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>43454</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43467</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43467</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43468</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43473</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43474</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43475</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>43475</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>43481</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>43481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>43482</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>43487</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>43487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>43487</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>43488</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>43493</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43494</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43496</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43501</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43506</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43508</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43511</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43514</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>43515</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>43517</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>43528</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43528</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43530</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43533</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43542</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43542</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43543</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>43558</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43563</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43573</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43578</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43579</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43579</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43580</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43584</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>43584</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>43584</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>43588</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>43589</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>43593</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>43594</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>43595</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>43599</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>43600</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>43602</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>43608</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>43612</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>43612</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43612</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>43619</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>43619</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>43621</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>43621</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>43626</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>43626</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>43634</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>43634</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>43636</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>43644</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>43647</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>43647</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>43649</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>43649</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>43651</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>43657</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>43657</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>43657</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>43661</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>43672</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>43679</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>43682</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>43683</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>43689</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43689</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43691</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>43698</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>43698</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>43699</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>43702</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>43703</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43711</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>43712</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43714</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43719</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43721</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>43725</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>43727</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>43727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>43727</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>43731</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>43740</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>43742</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>43748</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43748</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43756</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43762</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43765</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43766</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43767</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43773</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43773</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43773</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43775</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43781</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>43782</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43782</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43783</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43787</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>43795</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>43795</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>43796</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>43796</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>43796</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>43803</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>43809</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>43811</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>43850</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>43852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>43858</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>43858</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>43858</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>43858</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>43860</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43860</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43860</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>43860</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>43865</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>43866</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>43868</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>43868</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>43868</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43868</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43871</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43871</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43871</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43871</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43871</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43871</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43879</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>43882</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>43885</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>43886</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>43892</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43893</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>43893</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>43910</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>43914</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>43917</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>43924</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>43930</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>43936</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>43936</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>43936</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>43937</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>43938</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>43941</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>43956</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>43956</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>43956</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>43956</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>43956</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>43957</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>43957</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>43976</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>43977</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>43977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>43980</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>43980</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>43980</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>43990</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44000</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44007</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44008</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>44011</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44026</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44029</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44034</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44039</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44039</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44047</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44049</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44050</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44053</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44057</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44063</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44063</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44063</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44067</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44068</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>44069</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44069</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44076</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>44077</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44078</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44084</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44084</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44088</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44089</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44090</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44092</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44095</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>44099</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44100</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44104</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>44105</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44112</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>44112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>44112</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44112</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44112</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>44113</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44120</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44123</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44123</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44124</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>44125</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44130</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44140</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>44144</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44148</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44160</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44161</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44164</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44165</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44167</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44168</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44168</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44171</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44171</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44172</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>44187</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>44203</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>44203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>44203</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44207</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44215</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>44216</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44218</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>44218</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>44221</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44223</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44223</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44236</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44239</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44242</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44243</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44244</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44249</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44249</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44252</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44258</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>44266</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>44266</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44267</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>44272</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>44274</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>44278</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44284</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>44284</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>44294</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>44294</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>44308</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44309</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>44309</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>44313</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44314</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>44316</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>44319</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>44319</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>44319</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>44320</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>44322</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>44323</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>44326</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>44334</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>44334</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44335</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44337</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44337</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>44341</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>44354</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44357</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44361</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44375</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44375</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>44379</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44379</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44379</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44379</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44379</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44382</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>44383</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>44392</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>44411</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>44411</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>44416</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44418</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>44419</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>44425</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>44425</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>44425</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>44433</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>44434</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44435</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44439</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>44442</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>44445</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44447</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>44452</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>44452</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>44454</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>44454</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44454</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>44454</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44455</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>44456</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>44460</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44462</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44463</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44465</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44466</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44466</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44466</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44466</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44467</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44469</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44469</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44480</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44483</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44483</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>44483</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>44483</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>44483</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44484</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>44484</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44484</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44486</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>44487</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>44497</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>44500</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>44501</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>44502</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>44505</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>44516</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>44517</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>44517</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>44525</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>44539</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>44558</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44560</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>44567</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>44567</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>44568</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44575</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44578</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>44585</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>44587</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44587</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>44587</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>44587</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>44589</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>44594</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44596</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>44599</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>44600</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>44603</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>44606</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44608</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44608</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>44616</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>44616</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>44617</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>44623</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>44627</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44645</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>44650</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>44655</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>44657</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>44658</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>44677</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>44677</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>44687</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>44697</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>44699</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>44699</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>44699</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>44701</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>44704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>44714</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>44720</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>44725</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44728</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>44728</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44729</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44733</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44734</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44734</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44739</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>44739</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44739</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>44742</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>44743</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>44755</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>44776</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>44782</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>44782</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>44789</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>44795</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>44796</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44799</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44799</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44799</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44799</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44799</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44801</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44801</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44804</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44805</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44805</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>44805</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>44805</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44805</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44811</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44826</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>44830</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>44836</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44837</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44839</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>44846</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>44851</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>44852</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>44852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44854</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>44860</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44861</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44865</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>44868</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>44873</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44873</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>44874</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>44882</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>44882</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>44882</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>44882</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>44882</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>44886</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>44886</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>44886</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>44889</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44889</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>44890</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>44894</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44897</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>44897</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44907</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>44908</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>44918</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>44918</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>44918</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>44918</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44918</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>44918</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>44918</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44918</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>44918</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>44918</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>44918</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>44923</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>44924</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>44925</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>44930</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>44935</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>44935</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>44937</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>44937</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44939</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>44944</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>44949</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44949</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44949</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>44949</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44951</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>44952</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>44952</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44952</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>44952</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>44952</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44952</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>44952</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>44952</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>44953</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>44953</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>44956</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>44956</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>44958</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>44958</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>44958</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44959</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>44959</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>44960</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>44960</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>44963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44964</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44965</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>44967</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>44970</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>44974</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44974</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>44974</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>44977</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>44977</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>44977</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>44977</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>44978</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>44978</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>44978</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>44978</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>44981</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>44981</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44982</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>44982</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>44982</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>44984</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>44988</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44991</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>44991</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>44992</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>44992</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>44992</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44992</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>44993</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45000</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45000</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>45000</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45000</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45000</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45001</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45005</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>45005</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45007</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45007</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45007</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45007</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45008</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45009</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>45009</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45014</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45020</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45020</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45020</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45020</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45020</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45029</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45030</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45030</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45030</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45030</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45035</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>45035</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>45036</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45036</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45044</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45048</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45056</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45057</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45062</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45062</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45062</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45062</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45062</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45063</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45071</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45071</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45071</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>45076</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>45077</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45078</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45078</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45078</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45078</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45078</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45078</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45078</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45078</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45078</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45078</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45078</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45078</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45078</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45078</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45082</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45082</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45082</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45082</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45082</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45084</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>45085</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45086</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>45089</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45091</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>45091</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45091</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45093</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45093</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45096</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45096</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45097</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45097</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>45097</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>45098</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45098</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45098</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>45098</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>45098</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>45105</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48992,7 +48992,7 @@
         <v>45107</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49049,7 +49049,7 @@
         <v>45107</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45110</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>45111</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>45111</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>45111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45112</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45114</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45116</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45118</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45118</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45120</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45122</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45123</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45123</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45128</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45134</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45139</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45139</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45141</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45145</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45145</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45145</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45145</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45145</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45145</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45145</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45145</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45147</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45148</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45149</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45151</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45154</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45154</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>45159</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45160</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45160</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>45160</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45161</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45161</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45161</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>45162</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45163</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45163</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45163</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45163</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45166</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45166</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45166</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45167</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45168</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45169</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45171</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52618,7 +52618,7 @@
         <v>45174</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45174</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45174</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45174</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>45175</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>45175</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52960,7 +52960,7 @@
         <v>45176</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>45176</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>45176</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>45181</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>45182</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>45183</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>45184</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>45184</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>45187</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>45187</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45187</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45187</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45187</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45187</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45187</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45188</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45188</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45188</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45191</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>45194</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>45194</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45194</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45195</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         <v>45195</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         <v>45196</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45196</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45197</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45197</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45198</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54737,7 +54737,7 @@
         <v>45200</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
         <v>45199</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>45201</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45201</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>45201</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>45201</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55079,7 +55079,7 @@
         <v>45201</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55136,7 +55136,7 @@
         <v>45202</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         <v>45202</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         <v>45202</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45204</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>45209</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45210</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45211</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45215</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55597,7 +55597,7 @@
         <v>45216</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>45216</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45219</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45219</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45219</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45219</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45219</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>45222</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56053,7 +56053,7 @@
         <v>45222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45223</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45224</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56338,7 +56338,7 @@
         <v>45226</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56395,7 +56395,7 @@
         <v>45226</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>45226</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>45229</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45229</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56623,7 +56623,7 @@
         <v>45229</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45229</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45229</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45229</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45229</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56923,7 +56923,7 @@
         <v>45230</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56980,7 +56980,7 @@
         <v>45232</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57037,7 +57037,7 @@
         <v>45232</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45232</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57151,7 +57151,7 @@
         <v>45232</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>45232</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45232</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>45232</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>45232</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57436,7 +57436,7 @@
         <v>45235</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45235</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>45238</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>45240</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57664,7 +57664,7 @@
         <v>45240</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57835,7 +57835,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45245</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45245</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45245</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58120,7 +58120,7 @@
         <v>45246</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45246</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45246</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45246</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45247</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45247</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45250</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45250</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45250</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45254</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45257</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45257</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45257</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45259</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45260</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45260</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45260</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45260</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45260</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45260</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>45260</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59545,7 +59545,7 @@
         <v>45261</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59602,7 +59602,7 @@
         <v>45264</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59659,7 +59659,7 @@
         <v>45264</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45265</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45267</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45274</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45275</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60410,7 +60410,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60472,7 +60472,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45279</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60700,7 +60700,7 @@
         <v>45279</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>45279</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>45279</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60871,7 +60871,7 @@
         <v>45281</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60928,7 +60928,7 @@
         <v>45281</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>45290</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61042,7 +61042,7 @@
         <v>45294</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61099,7 +61099,7 @@
         <v>45299</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45301</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>45301</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61270,7 +61270,7 @@
         <v>45301</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45301</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61384,7 +61384,7 @@
         <v>45302</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45302</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>45303</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>45308</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61726,7 +61726,7 @@
         <v>45308</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         <v>45308</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61840,7 +61840,7 @@
         <v>45308</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61897,7 +61897,7 @@
         <v>45308</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62004,14 +62004,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 2638-2024</t>
+          <t>A 2758-2024</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62024,7 +62024,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -62061,14 +62061,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 2755-2024</t>
+          <t>A 2638-2024</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -62118,14 +62118,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 2759-2024</t>
+          <t>A 2765-2024</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62138,7 +62138,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -62175,14 +62175,14 @@
     <row r="1043" ht="15" customHeight="1">
       <c r="A1043" t="inlineStr">
         <is>
-          <t>A 2758-2024</t>
+          <t>A 2759-2024</t>
         </is>
       </c>
       <c r="B1043" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         </is>
       </c>
       <c r="G1043" t="n">
-        <v>9.699999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -62232,14 +62232,14 @@
     <row r="1044" ht="15" customHeight="1">
       <c r="A1044" t="inlineStr">
         <is>
-          <t>A 2765-2024</t>
+          <t>A 2755-2024</t>
         </is>
       </c>
       <c r="B1044" s="1" t="n">
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62252,7 +62252,7 @@
         </is>
       </c>
       <c r="G1044" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="H1044" t="n">
         <v>0</v>
@@ -62289,14 +62289,14 @@
     <row r="1045" ht="15" customHeight="1">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>A 2967-2024</t>
+          <t>A 2957-2024</t>
         </is>
       </c>
       <c r="B1045" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         </is>
       </c>
       <c r="G1045" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -62346,14 +62346,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 2957-2024</t>
+          <t>A 2969-2024</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62366,7 +62366,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -62403,14 +62403,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 2969-2024</t>
+          <t>A 2967-2024</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62423,7 +62423,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -62460,14 +62460,14 @@
     <row r="1048" ht="15" customHeight="1">
       <c r="A1048" t="inlineStr">
         <is>
-          <t>A 2897-2024</t>
+          <t>A 2966-2024</t>
         </is>
       </c>
       <c r="B1048" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62480,7 +62480,7 @@
         </is>
       </c>
       <c r="G1048" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -62517,14 +62517,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 2966-2024</t>
+          <t>A 2897-2024</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62537,7 +62537,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -62581,7 +62581,7 @@
         <v>45315</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62638,7 +62638,7 @@
         <v>45317</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62695,7 +62695,7 @@
         <v>45317</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62752,7 +62752,7 @@
         <v>45317</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62809,7 +62809,7 @@
         <v>45320</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62866,7 +62866,7 @@
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63037,7 +63037,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63094,7 +63094,7 @@
         <v>45323</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63151,7 +63151,7 @@
         <v>45324</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63208,7 +63208,7 @@
         <v>45327</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63265,7 +63265,7 @@
         <v>45327</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63379,7 +63379,7 @@
         <v>45330</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>45331</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>45331</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63550,7 +63550,7 @@
         <v>45333</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63600,14 +63600,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5707-2024</t>
+          <t>A 5706-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -63657,14 +63657,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5706-2024</t>
+          <t>A 5707-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -63714,14 +63714,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 6159-2024</t>
+          <t>A 6156-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63734,7 +63734,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -63771,14 +63771,14 @@
     <row r="1071" ht="15" customHeight="1">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>A 6156-2024</t>
+          <t>A 6159-2024</t>
         </is>
       </c>
       <c r="B1071" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63791,7 +63791,7 @@
         </is>
       </c>
       <c r="G1071" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="H1071" t="n">
         <v>0</v>
@@ -63828,14 +63828,14 @@
     <row r="1072" ht="15" customHeight="1">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>A 6546-2024</t>
+          <t>A 6545-2024</t>
         </is>
       </c>
       <c r="B1072" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63848,7 +63848,7 @@
         </is>
       </c>
       <c r="G1072" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H1072" t="n">
         <v>0</v>
@@ -63885,14 +63885,14 @@
     <row r="1073" ht="15" customHeight="1">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>A 6545-2024</t>
+          <t>A 6561-2024</t>
         </is>
       </c>
       <c r="B1073" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63905,7 +63905,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -63942,14 +63942,14 @@
     <row r="1074">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>A 6561-2024</t>
+          <t>A 6546-2024</t>
         </is>
       </c>
       <c r="B1074" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         </is>
       </c>
       <c r="G1074" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="H1074" t="n">
         <v>0</v>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -569,7 +569,7 @@
         <v>43345</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         <v>44826</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44872</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44575</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>44575</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44088</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44484</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44974</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>44340</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44743</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44958</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45201</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>43315</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45196</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>45208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45301</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>43320</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>43353</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>43474</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43475</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43523</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>43524</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>43531</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43585</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43807</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>43809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>43879</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>43990</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44092</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44235</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44342</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44435</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44608</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44636</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44642</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44690</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44706</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44754</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44801</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44914</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44960</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44974</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45007</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45049</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45093</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45093</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45093</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45093</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45216</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45294</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>43320</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>43321</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>43321</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>43325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>43328</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>43335</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>43336</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>43336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>43340</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>43341</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>43346</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>43348</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>43355</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>43356</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>43356</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>43357</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>43368</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>43375</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>43376</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>43383</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>43385</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>43388</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>43395</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>43395</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>43402</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>43402</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>43402</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>43402</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>43406</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>43411</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>43412</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>43414</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43423</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43423</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>43426</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43440</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43441</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43441</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>43441</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>43441</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43441</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>43445</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>43445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>43445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>43446</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>43454</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>43454</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43467</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43467</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43468</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43473</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43474</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43475</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>43475</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>43481</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>43481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>43482</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>43487</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>43487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>43487</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>43488</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>43493</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43494</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43496</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43501</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43506</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43508</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43511</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43514</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>43515</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>43517</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>43528</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43528</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43530</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43533</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43542</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43542</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43543</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>43558</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43563</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43573</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43578</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43579</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43579</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43580</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43584</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>43584</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>43584</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>43588</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>43589</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>43593</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>43594</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>43595</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>43599</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>43600</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>43602</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>43608</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>43612</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>43612</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43612</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>43619</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>43619</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>43621</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>43621</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>43626</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>43626</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>43634</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>43634</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>43636</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>43644</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>43647</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>43647</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>43649</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>43649</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>43651</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>43657</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>43657</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>43657</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>43661</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>43672</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>43679</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>43682</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>43683</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>43689</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43689</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43691</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>43698</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>43698</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>43699</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>43702</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>43703</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43711</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>43712</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43714</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43719</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43721</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>43725</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>43727</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>43727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>43727</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>43731</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>43740</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>43742</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>43748</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43748</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43756</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43762</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43765</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43766</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43767</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43773</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43773</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43773</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43775</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43781</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>43782</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43782</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43783</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43787</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>43795</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>43795</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>43796</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>43796</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>43796</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>43803</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>43809</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>43811</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>43850</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>43852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>43858</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>43858</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>43858</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>43858</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>43860</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43860</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43860</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>43860</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>43865</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>43866</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>43868</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>43868</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>43868</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43868</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43871</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43871</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43871</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43871</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43871</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43871</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43879</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>43882</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>43885</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>43886</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>43892</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43893</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>43893</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>43910</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>43914</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>43917</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>43924</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>43930</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>43936</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>43936</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>43936</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>43937</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>43938</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>43941</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>43956</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>43956</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>43956</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>43956</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>43956</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>43957</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>43957</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>43976</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>43977</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>43977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>43980</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>43980</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>43980</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>43990</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44000</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44007</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44008</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>44011</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44026</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44029</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44034</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44039</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44039</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44047</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44049</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44050</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44053</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44057</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44063</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44063</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44063</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44067</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44068</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>44069</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44069</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44076</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>44077</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44078</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44084</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44084</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44088</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44089</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44090</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44092</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44095</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>44099</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44100</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44104</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>44105</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44112</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>44112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>44112</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44112</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44112</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>44113</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44120</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44123</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44123</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44124</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>44125</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44130</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44140</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>44144</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44148</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44160</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44161</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44164</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44165</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44167</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44168</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44168</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44171</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44171</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44172</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>44187</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>44203</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>44203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>44203</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44207</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44215</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>44216</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44218</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>44218</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>44221</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44223</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44223</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44236</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44239</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44242</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44243</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44244</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44249</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44249</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44252</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44258</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>44266</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>44266</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44267</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>44272</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>44274</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>44278</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44284</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>44284</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>44294</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>44294</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>44308</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44309</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>44309</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>44313</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44314</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>44316</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>44319</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>44319</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>44319</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>44320</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>44322</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>44323</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>44326</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>44334</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>44334</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44335</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44337</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44337</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>44341</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>44354</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44357</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44361</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44375</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44375</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>44379</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44379</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44379</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44379</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44379</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44382</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>44383</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>44392</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>44411</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>44411</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>44416</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44418</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>44419</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>44425</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>44425</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>44425</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>44433</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>44434</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44435</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44439</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>44442</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>44445</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44447</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>44452</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>44452</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>44454</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>44454</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44454</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>44454</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44455</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>44456</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>44460</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44462</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44463</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44465</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44466</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44466</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44466</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44466</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44467</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44469</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44469</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44480</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44483</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44483</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>44483</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>44483</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>44483</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44484</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>44484</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44484</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44486</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>44487</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>44497</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>44500</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>44501</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>44502</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>44505</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>44516</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>44517</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>44517</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>44525</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>44539</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>44558</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44560</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>44567</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>44567</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>44568</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44575</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44578</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>44585</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>44587</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44587</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>44587</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>44587</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>44589</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>44594</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44596</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>44599</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>44600</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>44603</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>44606</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44608</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44608</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>44616</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>44616</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>44617</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>44623</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>44627</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44645</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>44650</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>44655</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>44657</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>44658</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>44677</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>44677</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>44687</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>44697</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>44699</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>44699</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>44699</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>44701</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>44704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>44714</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>44720</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>44725</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44728</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>44728</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44729</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44733</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44734</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44734</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44739</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>44739</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44739</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>44742</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>44743</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>44755</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>44776</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>44782</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>44782</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>44789</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>44795</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>44796</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44799</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44799</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44799</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44799</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44799</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44801</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44801</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44804</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44805</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44805</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>44805</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>44805</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44805</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44811</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44826</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>44830</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>44836</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44837</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44839</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>44846</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>44851</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>44852</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>44852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44854</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>44860</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44861</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44865</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>44868</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>44873</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44873</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>44874</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>44882</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>44882</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>44882</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>44882</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>44882</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>44886</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>44886</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>44886</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>44889</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44889</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>44890</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>44894</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44897</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>44897</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44907</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>44908</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>44918</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>44918</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>44918</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>44918</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44918</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>44918</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>44918</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44918</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>44918</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>44918</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>44918</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>44923</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>44924</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>44925</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>44930</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>44935</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>44935</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>44937</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>44937</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44939</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>44944</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>44949</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44949</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44949</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>44949</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44951</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>44952</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>44952</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44952</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>44952</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>44952</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44952</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>44952</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>44952</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>44953</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>44953</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>44956</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>44956</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>44958</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>44958</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>44958</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44959</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>44959</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>44960</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>44960</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>44963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44964</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44965</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>44967</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>44970</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>44974</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44974</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>44974</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>44977</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>44977</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>44977</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>44977</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>44978</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>44978</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>44978</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>44978</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>44981</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>44981</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44982</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>44982</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>44982</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>44984</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>44988</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44991</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>44991</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>44992</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>44992</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>44992</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44992</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>44993</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45000</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45000</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>45000</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45000</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45000</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45001</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45005</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>45005</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45007</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45007</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45007</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45007</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45008</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45009</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>45009</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45014</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45020</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45020</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45020</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45020</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45020</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45029</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45030</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45030</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45030</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45030</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45035</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>45035</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>45036</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45036</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45044</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45048</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45056</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45057</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45062</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45062</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45062</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45062</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45062</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45063</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45071</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45071</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45071</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>45076</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>45077</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45078</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45078</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45078</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45078</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45078</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45078</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45078</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45078</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45078</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45078</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45078</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45078</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45078</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45078</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45082</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45082</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45082</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45082</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45082</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45084</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>45085</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45086</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>45089</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45091</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>45091</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45091</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45093</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45093</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45096</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45096</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45097</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45097</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>45097</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>45098</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45098</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45098</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>45098</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>45098</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>45105</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48992,7 +48992,7 @@
         <v>45107</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49049,7 +49049,7 @@
         <v>45107</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45110</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>45111</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>45111</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>45111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45112</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45114</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45116</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45118</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45118</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45120</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45122</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45123</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45123</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45128</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45134</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45139</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45139</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45141</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45145</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45145</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45145</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45145</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45145</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45145</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45145</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45145</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45147</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45148</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45149</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45151</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45154</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45154</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>45159</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45160</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45160</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>45160</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45161</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45161</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45161</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>45162</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45163</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45163</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45163</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45163</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45166</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45166</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45166</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45167</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45168</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45169</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45171</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52618,7 +52618,7 @@
         <v>45174</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45174</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45174</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45174</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>45175</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>45175</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52960,7 +52960,7 @@
         <v>45176</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>45176</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>45176</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>45181</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>45182</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>45183</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>45184</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>45184</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>45187</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>45187</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45187</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45187</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45187</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45187</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45187</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45188</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45188</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45188</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45191</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>45194</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>45194</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45194</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45195</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         <v>45195</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         <v>45196</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45196</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45197</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45197</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45198</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54737,7 +54737,7 @@
         <v>45200</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
         <v>45199</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>45201</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45201</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>45201</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>45201</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55079,7 +55079,7 @@
         <v>45201</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55136,7 +55136,7 @@
         <v>45202</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         <v>45202</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         <v>45202</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45204</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>45209</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45210</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45211</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45215</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55597,7 +55597,7 @@
         <v>45216</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>45216</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45219</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45219</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45219</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45219</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45219</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>45222</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56053,7 +56053,7 @@
         <v>45222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45223</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45224</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56338,7 +56338,7 @@
         <v>45226</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56395,7 +56395,7 @@
         <v>45226</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>45226</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>45229</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45229</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56623,7 +56623,7 @@
         <v>45229</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45229</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45229</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45229</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45229</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56923,7 +56923,7 @@
         <v>45230</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56980,7 +56980,7 @@
         <v>45232</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57037,7 +57037,7 @@
         <v>45232</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45232</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57151,7 +57151,7 @@
         <v>45232</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>45232</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45232</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>45232</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>45232</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57436,7 +57436,7 @@
         <v>45235</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45235</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>45238</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>45240</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57664,7 +57664,7 @@
         <v>45240</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57835,7 +57835,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45245</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45245</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45245</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58120,7 +58120,7 @@
         <v>45246</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45246</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45246</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45246</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45247</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45247</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45250</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45250</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45250</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45254</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45257</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45257</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45257</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45259</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45260</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45260</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45260</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45260</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45260</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45260</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>45260</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59545,7 +59545,7 @@
         <v>45261</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59602,7 +59602,7 @@
         <v>45264</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59659,7 +59659,7 @@
         <v>45264</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45265</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45267</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45274</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45275</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60410,7 +60410,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60472,7 +60472,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45279</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60700,7 +60700,7 @@
         <v>45279</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>45279</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>45279</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60871,7 +60871,7 @@
         <v>45281</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60928,7 +60928,7 @@
         <v>45281</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>45290</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61042,7 +61042,7 @@
         <v>45294</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61099,7 +61099,7 @@
         <v>45299</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45301</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>45301</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61270,7 +61270,7 @@
         <v>45301</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45301</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61384,7 +61384,7 @@
         <v>45302</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45302</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>45303</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>45308</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61726,7 +61726,7 @@
         <v>45308</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         <v>45308</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61840,7 +61840,7 @@
         <v>45308</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61897,7 +61897,7 @@
         <v>45308</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>45314</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62068,7 +62068,7 @@
         <v>45314</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62125,7 +62125,7 @@
         <v>45314</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62182,7 +62182,7 @@
         <v>45314</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62289,14 +62289,14 @@
     <row r="1045" ht="15" customHeight="1">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>A 2957-2024</t>
+          <t>A 2952-2024</t>
         </is>
       </c>
       <c r="B1045" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         </is>
       </c>
       <c r="G1045" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -62346,14 +62346,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 2969-2024</t>
+          <t>A 2957-2024</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62366,7 +62366,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -62403,14 +62403,14 @@
     <row r="1047" ht="15" customHeight="1">
       <c r="A1047" t="inlineStr">
         <is>
-          <t>A 2967-2024</t>
+          <t>A 2969-2024</t>
         </is>
       </c>
       <c r="B1047" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62423,7 +62423,7 @@
         </is>
       </c>
       <c r="G1047" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="H1047" t="n">
         <v>0</v>
@@ -62467,7 +62467,7 @@
         <v>45315</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62524,7 +62524,7 @@
         <v>45315</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62574,14 +62574,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 2952-2024</t>
+          <t>A 2967-2024</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45315</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -62631,14 +62631,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 3379-2024</t>
+          <t>A 3380-2024</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62651,7 +62651,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -62688,14 +62688,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 3380-2024</t>
+          <t>A 3379-2024</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62708,7 +62708,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -62752,7 +62752,7 @@
         <v>45317</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62809,7 +62809,7 @@
         <v>45320</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62866,7 +62866,7 @@
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62923,7 +62923,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62980,7 +62980,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63037,7 +63037,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63094,7 +63094,7 @@
         <v>45323</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63151,7 +63151,7 @@
         <v>45324</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63201,14 +63201,14 @@
     <row r="1061" ht="15" customHeight="1">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>A 4432-2024</t>
+          <t>A 4433-2024</t>
         </is>
       </c>
       <c r="B1061" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63221,7 +63221,7 @@
         </is>
       </c>
       <c r="G1061" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -63258,14 +63258,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 4433-2024</t>
+          <t>A 4432-2024</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63278,7 +63278,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -63322,7 +63322,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63379,7 +63379,7 @@
         <v>45330</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>45331</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>45331</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63550,7 +63550,7 @@
         <v>45333</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63600,14 +63600,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5706-2024</t>
+          <t>A 5707-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -63657,14 +63657,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5707-2024</t>
+          <t>A 5706-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -63721,7 +63721,7 @@
         <v>45337</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45337</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45341</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45341</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45341</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -569,7 +569,7 @@
         <v>43345</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         <v>44826</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44872</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44575</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>44575</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44088</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44484</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44974</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>44340</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44743</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44958</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45201</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>43315</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45196</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>45208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45301</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>43320</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>43353</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>43474</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43475</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43523</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>43524</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>43531</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43585</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43807</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>43809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>43879</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>43990</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44092</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44235</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44342</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44435</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44608</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44636</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44642</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44690</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44706</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44754</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44801</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44914</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44960</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44974</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45007</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45049</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45093</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45093</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45093</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45093</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45216</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45294</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>43320</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>43321</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>43321</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>43325</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>43328</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>43335</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>43336</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>43336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>43340</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>43341</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>43346</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>43348</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>43355</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>43356</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>43356</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>43357</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>43368</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>43375</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>43376</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>43383</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         <v>43385</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>43388</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>43395</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>43395</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>43402</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>43402</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>43402</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>43402</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>43406</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>43411</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>43412</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>43414</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>43419</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>43423</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>43423</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>43424</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>43426</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>43438</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>43440</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>43441</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>43441</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>43441</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>43441</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>43441</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>43445</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>43445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>43445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43446</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>43446</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>43454</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>43454</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>43467</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>43467</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>43468</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>43468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>43473</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>43474</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>43475</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>43475</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>43481</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>43481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>43482</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>43487</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>43487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>43487</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>43488</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>43493</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>43494</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>43496</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>43496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>43501</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>43506</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>43508</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>43511</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>43514</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>43515</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>43517</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>43528</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>43528</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43530</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43533</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43542</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43542</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43543</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>43557</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>43558</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>43563</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>43573</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>43578</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>43579</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>43579</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>43580</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>43584</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>43584</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>43584</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>43588</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>43589</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>43593</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>43594</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11766,7 +11766,7 @@
         <v>43595</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>43599</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>43600</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>43602</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>43608</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>43612</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>43612</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43612</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>43619</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>43619</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>43621</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>43621</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>43626</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>43626</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>43634</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>43634</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>43636</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>43644</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>43647</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>43647</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>43649</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>43649</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>43651</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>43657</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>43657</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>43657</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>43661</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>43672</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>43679</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>43682</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>43683</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>43685</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>43689</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>43689</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>43691</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>43696</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13994,7 +13994,7 @@
         <v>43698</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>43698</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>43699</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>43702</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>43703</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>43705</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>43706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>43707</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>43710</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>43711</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>43712</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>43714</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>43719</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>43721</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>43725</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15144,7 +15144,7 @@
         <v>43727</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>43727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>43727</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>43731</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>43735</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>43740</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>43742</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>43748</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>43748</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>43756</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>43762</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>43762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>43765</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>43766</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>43767</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>43773</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>43773</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>43773</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>43775</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>43781</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>43782</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>43782</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>43783</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>43787</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>43795</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>43795</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>43796</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>43796</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>43796</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>43803</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>43809</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>43811</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>43840</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>43843</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>43850</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>43852</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>43858</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>43858</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>43858</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>43858</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>43860</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43860</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>43860</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>43860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17900,7 +17900,7 @@
         <v>43860</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>43865</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>43866</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>43868</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>43868</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>43868</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>43868</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>43871</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>43871</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>43871</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>43871</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>43871</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>43871</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>43879</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>43882</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>43885</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>43886</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18879,7 +18879,7 @@
         <v>43892</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43893</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>43893</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>43910</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>43914</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>43915</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>43917</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>43923</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>43924</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>43930</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>43936</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>43936</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>43936</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19635,7 +19635,7 @@
         <v>43937</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>43938</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>43941</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>43956</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>43956</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>43956</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>43956</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>43956</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>43957</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>43957</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20220,7 +20220,7 @@
         <v>43976</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>43977</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>43977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>43980</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>43980</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>43980</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>43990</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44000</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44007</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>44008</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>44011</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44026</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20986,7 +20986,7 @@
         <v>44029</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44034</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44039</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         <v>44039</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>44047</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44049</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>44050</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>44053</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44057</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>44063</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>44063</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44063</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44067</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>44068</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>44069</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44069</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44076</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>44077</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44078</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>44084</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>44084</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>44088</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44089</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>44090</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44092</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44095</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>44099</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>44100</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44104</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>44105</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44112</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22783,7 +22783,7 @@
         <v>44112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>44112</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22897,7 +22897,7 @@
         <v>44112</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22954,7 +22954,7 @@
         <v>44112</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>44113</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>44120</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44123</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>44123</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44124</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>44125</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44130</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44140</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>44144</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>44148</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>44160</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>44161</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>44164</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>44165</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44167</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>44168</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44168</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44171</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>44171</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44172</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24156,7 +24156,7 @@
         <v>44187</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>44203</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>44203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>44203</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>44207</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44215</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>44216</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44218</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>44218</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>44221</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44223</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44223</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44236</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44239</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44242</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44243</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>44244</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44249</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44249</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44252</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>44258</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>44266</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>44266</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>44267</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>44272</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25586,7 +25586,7 @@
         <v>44274</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>44278</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>44284</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>44284</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>44294</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>44294</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>44308</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44309</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>44309</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>44313</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>44314</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26213,7 +26213,7 @@
         <v>44316</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>44319</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26327,7 +26327,7 @@
         <v>44319</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26384,7 +26384,7 @@
         <v>44319</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26441,7 +26441,7 @@
         <v>44320</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>44322</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>44323</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>44326</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>44334</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>44334</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44335</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>44337</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44337</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>44341</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>44354</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27068,7 +27068,7 @@
         <v>44357</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44357</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>44361</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>44362</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>44364</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44375</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44375</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>44379</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44379</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44379</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44379</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44379</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44382</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>44383</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>44392</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>44411</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>44411</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>44416</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44418</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         <v>44419</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28233,7 +28233,7 @@
         <v>44419</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>44425</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>44425</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
         <v>44425</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>44433</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>44433</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>44434</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44435</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44439</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>44442</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>44445</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>44446</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29036,7 +29036,7 @@
         <v>44447</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>44452</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>44452</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>44454</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>44454</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44454</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>44454</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44455</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>44456</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>44460</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44462</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29673,7 +29673,7 @@
         <v>44463</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>44463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29787,7 +29787,7 @@
         <v>44465</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29844,7 +29844,7 @@
         <v>44466</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44466</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44466</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>44466</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44467</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44469</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44469</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44480</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44483</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44483</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>44483</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>44483</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>44483</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44484</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>44484</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30756,7 +30756,7 @@
         <v>44484</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44486</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30870,7 +30870,7 @@
         <v>44487</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>44497</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>44500</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>44501</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>44502</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>44505</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>44516</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>44517</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>44517</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>44525</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>44539</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>44558</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>44560</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>44567</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>44567</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>44568</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44575</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44578</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>44585</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>44587</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44587</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>44587</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>44587</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>44589</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>44594</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>44596</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>44599</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>44600</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>44603</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>44606</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44608</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>44608</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32704,7 +32704,7 @@
         <v>44616</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>44616</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>44617</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32875,7 +32875,7 @@
         <v>44623</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>44627</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44645</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33103,7 +33103,7 @@
         <v>44650</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>44655</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>44657</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>44658</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>44677</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>44677</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>44687</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33507,7 +33507,7 @@
         <v>44697</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33564,7 +33564,7 @@
         <v>44699</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>44699</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>44699</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>44701</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>44704</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>44714</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>44720</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>44721</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>44725</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44728</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>44728</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44729</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44732</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44733</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44734</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44734</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44739</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>44739</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44739</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>44742</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>44743</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>44743</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>44755</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>44776</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>44782</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>44782</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>44789</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>44795</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>44796</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>44799</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44799</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>44799</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>44799</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>44799</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>44801</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44801</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>44802</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>44804</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44805</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44805</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>44805</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>44805</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44805</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44811</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>44818</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>44826</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>44830</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36305,7 +36305,7 @@
         <v>44836</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44837</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36419,7 +36419,7 @@
         <v>44839</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36476,7 +36476,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36533,7 +36533,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36590,7 +36590,7 @@
         <v>44846</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36647,7 +36647,7 @@
         <v>44851</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>44851</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>44852</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>44852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>44852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>44854</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>44860</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>44861</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37160,7 +37160,7 @@
         <v>44865</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>44868</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>44868</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>44873</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>44873</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>44874</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37502,7 +37502,7 @@
         <v>44882</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>44882</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>44882</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>44882</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>44882</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>44886</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>44886</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37901,7 +37901,7 @@
         <v>44886</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>44889</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44889</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>44890</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>44894</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>44897</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>44897</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38315,7 +38315,7 @@
         <v>44907</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>44908</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>44918</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38486,7 +38486,7 @@
         <v>44918</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>44918</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>44918</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38657,7 +38657,7 @@
         <v>44918</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>44918</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>44918</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>44918</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>44918</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>44918</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>44918</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>44923</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>44924</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>44925</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>44930</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>44935</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>44935</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>44937</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>44937</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>44939</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>44944</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>44949</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>44949</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         <v>44949</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>44949</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44951</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>44952</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>44952</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>44952</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>44952</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>44952</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40382,7 +40382,7 @@
         <v>44952</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>44952</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>44952</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>44953</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40610,7 +40610,7 @@
         <v>44953</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>44956</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40724,7 +40724,7 @@
         <v>44956</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40781,7 +40781,7 @@
         <v>44958</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>44958</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40895,7 +40895,7 @@
         <v>44958</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40952,7 +40952,7 @@
         <v>44959</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>44959</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41066,7 +41066,7 @@
         <v>44960</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>44960</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>44963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41237,7 +41237,7 @@
         <v>44963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>44964</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>44965</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41408,7 +41408,7 @@
         <v>44967</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41465,7 +41465,7 @@
         <v>44970</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41522,7 +41522,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>44972</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41693,7 +41693,7 @@
         <v>44974</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>44974</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44974</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>44974</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>44977</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42045,7 +42045,7 @@
         <v>44977</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>44977</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>44977</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42216,7 +42216,7 @@
         <v>44978</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>44978</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>44978</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>44978</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>44981</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>44981</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42558,7 +42558,7 @@
         <v>44982</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>44982</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42672,7 +42672,7 @@
         <v>44982</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42729,7 +42729,7 @@
         <v>44984</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>44985</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>44988</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>44991</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>44991</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>44992</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>44992</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43128,7 +43128,7 @@
         <v>44992</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         <v>44992</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43242,7 +43242,7 @@
         <v>44993</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>44998</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43356,7 +43356,7 @@
         <v>45000</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43413,7 +43413,7 @@
         <v>45000</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43470,7 +43470,7 @@
         <v>45000</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43527,7 +43527,7 @@
         <v>45000</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43812,7 +43812,7 @@
         <v>45000</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45001</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43926,7 +43926,7 @@
         <v>45005</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>45005</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44040,7 +44040,7 @@
         <v>45007</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44097,7 +44097,7 @@
         <v>45007</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45007</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45007</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>45008</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45009</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>45009</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45014</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44496,7 +44496,7 @@
         <v>45020</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45020</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45020</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45020</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45020</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45029</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45030</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45030</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45030</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45030</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45035</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>45035</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>45036</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>45036</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45037</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>45042</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45542,7 +45542,7 @@
         <v>45044</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45048</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45049</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45713,7 +45713,7 @@
         <v>45056</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>45057</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45062</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45884,7 +45884,7 @@
         <v>45062</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>45062</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45062</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45062</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>45063</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46226,7 +46226,7 @@
         <v>45071</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45071</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46397,7 +46397,7 @@
         <v>45071</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>45076</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46511,7 +46511,7 @@
         <v>45077</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>45078</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45078</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>45078</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45078</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45078</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46868,7 +46868,7 @@
         <v>45078</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46925,7 +46925,7 @@
         <v>45078</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>45078</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         <v>45078</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45078</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>45078</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45078</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45078</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45078</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45082</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47443,7 +47443,7 @@
         <v>45082</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45082</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47671,7 +47671,7 @@
         <v>45082</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45082</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45084</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>45085</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47899,7 +47899,7 @@
         <v>45086</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47956,7 +47956,7 @@
         <v>45089</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45091</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>45091</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45091</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48251,7 +48251,7 @@
         <v>45093</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48308,7 +48308,7 @@
         <v>45093</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45096</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48422,7 +48422,7 @@
         <v>45096</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45097</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>45097</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>45097</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>45098</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45098</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45098</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48821,7 +48821,7 @@
         <v>45098</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>45098</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>45105</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48992,7 +48992,7 @@
         <v>45107</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49049,7 +49049,7 @@
         <v>45107</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49106,7 +49106,7 @@
         <v>45110</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>45111</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>45111</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>45111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>45111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49448,7 +49448,7 @@
         <v>45112</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>45114</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>45116</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49619,7 +49619,7 @@
         <v>45118</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>45118</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49733,7 +49733,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>45119</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>45120</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>45122</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>45123</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45123</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50075,7 +50075,7 @@
         <v>45128</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50132,7 +50132,7 @@
         <v>45134</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50189,7 +50189,7 @@
         <v>45139</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50246,7 +50246,7 @@
         <v>45139</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45141</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45145</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>45145</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45145</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45145</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45145</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45145</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50702,7 +50702,7 @@
         <v>45145</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45145</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50816,7 +50816,7 @@
         <v>45147</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45148</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50930,7 +50930,7 @@
         <v>45148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45149</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51044,7 +51044,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51101,7 +51101,7 @@
         <v>45151</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>45153</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>45154</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45154</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51401,7 +51401,7 @@
         <v>45159</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51458,7 +51458,7 @@
         <v>45160</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51515,7 +51515,7 @@
         <v>45160</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45160</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         <v>45160</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51691,7 +51691,7 @@
         <v>45161</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>45161</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>45161</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>45162</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51924,7 +51924,7 @@
         <v>45163</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51981,7 +51981,7 @@
         <v>45163</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52038,7 +52038,7 @@
         <v>45163</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>45163</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52152,7 +52152,7 @@
         <v>45166</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52209,7 +52209,7 @@
         <v>45166</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45166</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52323,7 +52323,7 @@
         <v>45167</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52380,7 +52380,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45168</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52499,7 +52499,7 @@
         <v>45169</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45171</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52618,7 +52618,7 @@
         <v>45174</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52675,7 +52675,7 @@
         <v>45174</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45174</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52789,7 +52789,7 @@
         <v>45174</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52846,7 +52846,7 @@
         <v>45175</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>45175</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52960,7 +52960,7 @@
         <v>45176</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53017,7 +53017,7 @@
         <v>45176</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>45176</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>45181</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53188,7 +53188,7 @@
         <v>45182</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53245,7 +53245,7 @@
         <v>45183</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>45184</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>45184</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>45187</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53478,7 +53478,7 @@
         <v>45187</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53535,7 +53535,7 @@
         <v>45187</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53592,7 +53592,7 @@
         <v>45187</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>45187</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53706,7 +53706,7 @@
         <v>45187</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53763,7 +53763,7 @@
         <v>45187</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53820,7 +53820,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>45188</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53934,7 +53934,7 @@
         <v>45188</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53991,7 +53991,7 @@
         <v>45188</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54048,7 +54048,7 @@
         <v>45191</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>45194</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>45194</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45194</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45195</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         <v>45195</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         <v>45196</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54452,7 +54452,7 @@
         <v>45196</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54509,7 +54509,7 @@
         <v>45197</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54566,7 +54566,7 @@
         <v>45197</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45198</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54680,7 +54680,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54737,7 +54737,7 @@
         <v>45200</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54794,7 +54794,7 @@
         <v>45199</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>45201</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54908,7 +54908,7 @@
         <v>45201</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54965,7 +54965,7 @@
         <v>45201</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>45201</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55079,7 +55079,7 @@
         <v>45201</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55136,7 +55136,7 @@
         <v>45202</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55193,7 +55193,7 @@
         <v>45202</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55250,7 +55250,7 @@
         <v>45202</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45204</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>45209</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>45210</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45211</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45215</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55597,7 +55597,7 @@
         <v>45216</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55654,7 +55654,7 @@
         <v>45216</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55711,7 +55711,7 @@
         <v>45219</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45219</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45219</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45219</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55939,7 +55939,7 @@
         <v>45219</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55996,7 +55996,7 @@
         <v>45222</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56053,7 +56053,7 @@
         <v>45222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45223</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45224</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45225</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56338,7 +56338,7 @@
         <v>45226</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56395,7 +56395,7 @@
         <v>45226</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56452,7 +56452,7 @@
         <v>45226</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56509,7 +56509,7 @@
         <v>45229</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>45229</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56623,7 +56623,7 @@
         <v>45229</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>45229</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45229</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56804,7 +56804,7 @@
         <v>45229</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45229</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56923,7 +56923,7 @@
         <v>45230</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -56980,7 +56980,7 @@
         <v>45232</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57037,7 +57037,7 @@
         <v>45232</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45232</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57151,7 +57151,7 @@
         <v>45232</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>45232</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57265,7 +57265,7 @@
         <v>45232</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>45232</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>45232</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57436,7 +57436,7 @@
         <v>45235</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57493,7 +57493,7 @@
         <v>45235</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>45238</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>45240</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57664,7 +57664,7 @@
         <v>45240</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>45245</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57835,7 +57835,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45245</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45245</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45245</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58120,7 +58120,7 @@
         <v>45246</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45246</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58234,7 +58234,7 @@
         <v>45246</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45246</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45247</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>45247</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58462,7 +58462,7 @@
         <v>45250</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         <v>45250</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58576,7 +58576,7 @@
         <v>45250</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58633,7 +58633,7 @@
         <v>45253</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58747,7 +58747,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58861,7 +58861,7 @@
         <v>45254</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58918,7 +58918,7 @@
         <v>45257</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>45257</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59032,7 +59032,7 @@
         <v>45257</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59089,7 +59089,7 @@
         <v>45259</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45260</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45260</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45260</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45260</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45260</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45260</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>45260</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59545,7 +59545,7 @@
         <v>45261</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59602,7 +59602,7 @@
         <v>45264</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59659,7 +59659,7 @@
         <v>45264</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45265</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45266</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59887,7 +59887,7 @@
         <v>45267</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59949,7 +59949,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>45267</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>45271</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45274</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60348,7 +60348,7 @@
         <v>45275</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60410,7 +60410,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60472,7 +60472,7 @@
         <v>45279</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45279</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60700,7 +60700,7 @@
         <v>45279</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>45279</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>45279</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60871,7 +60871,7 @@
         <v>45281</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60928,7 +60928,7 @@
         <v>45281</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>45290</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61042,7 +61042,7 @@
         <v>45294</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61099,7 +61099,7 @@
         <v>45299</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45301</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>45301</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61270,7 +61270,7 @@
         <v>45301</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45301</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61384,7 +61384,7 @@
         <v>45302</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45302</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>45303</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>45307</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>45308</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61726,7 +61726,7 @@
         <v>45308</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         <v>45308</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61840,7 +61840,7 @@
         <v>45308</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61897,7 +61897,7 @@
         <v>45308</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>45310</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>45314</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62068,7 +62068,7 @@
         <v>45314</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62125,7 +62125,7 @@
         <v>45314</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62182,7 +62182,7 @@
         <v>45314</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62239,7 +62239,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62296,7 +62296,7 @@
         <v>45315</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62353,7 +62353,7 @@
         <v>45315</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62410,7 +62410,7 @@
         <v>45315</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62467,7 +62467,7 @@
         <v>45315</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62524,7 +62524,7 @@
         <v>45315</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62581,7 +62581,7 @@
         <v>45315</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62638,7 +62638,7 @@
         <v>45317</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62695,7 +62695,7 @@
         <v>45317</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62752,7 +62752,7 @@
         <v>45317</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62809,7 +62809,7 @@
         <v>45320</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62859,14 +62859,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 3820-2024</t>
+          <t>A 3761-2024</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62879,7 +62879,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -62916,14 +62916,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 3761-2024</t>
+          <t>A 3765-2024</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -62936,7 +62936,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>4.7</v>
+        <v>10.2</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -62973,14 +62973,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 3765-2024</t>
+          <t>A 3823-2024</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -62993,7 +62993,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>10.2</v>
+        <v>4.9</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -63030,14 +63030,14 @@
     <row r="1058" ht="15" customHeight="1">
       <c r="A1058" t="inlineStr">
         <is>
-          <t>A 3823-2024</t>
+          <t>A 3820-2024</t>
         </is>
       </c>
       <c r="B1058" s="1" t="n">
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63050,7 +63050,7 @@
         </is>
       </c>
       <c r="G1058" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="H1058" t="n">
         <v>0</v>
@@ -63094,7 +63094,7 @@
         <v>45323</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63151,7 +63151,7 @@
         <v>45324</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63201,14 +63201,14 @@
     <row r="1061" ht="15" customHeight="1">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>A 4432-2024</t>
+          <t>A 4433-2024</t>
         </is>
       </c>
       <c r="B1061" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63221,7 +63221,7 @@
         </is>
       </c>
       <c r="G1061" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -63258,14 +63258,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 4433-2024</t>
+          <t>A 4432-2024</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63278,7 +63278,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -63322,7 +63322,7 @@
         <v>45329</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63379,7 +63379,7 @@
         <v>45330</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63436,7 +63436,7 @@
         <v>45331</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>45331</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63550,7 +63550,7 @@
         <v>45333</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63607,7 +63607,7 @@
         <v>45334</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63664,7 +63664,7 @@
         <v>45334</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63721,7 +63721,7 @@
         <v>45337</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63778,7 +63778,7 @@
         <v>45337</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45341</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63892,7 +63892,7 @@
         <v>45341</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63949,7 +63949,7 @@
         <v>45341</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64006,7 +64006,7 @@
         <v>45346</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -569,7 +569,7 @@
         <v>43345</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         <v>44826</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44872</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44575</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>44575</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44088</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44484</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44974</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>44340</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44743</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44958</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45201</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>43315</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45196</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>45208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45301</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>43320</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>43353</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>43474</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43475</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43523</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>43524</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>43531</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43585</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43807</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>43809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>43879</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>43990</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44092</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44235</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44342</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44435</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44608</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44636</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44642</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44690</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44706</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44754</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44801</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44914</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44960</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44974</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45007</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45049</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45093</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45093</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45093</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45093</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45216</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45294</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45348</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>43320</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>43321</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43321</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43325</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43328</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43335</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43336</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43340</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43341</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43346</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43348</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43355</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43356</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43356</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43357</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43368</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43375</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>43376</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>43383</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>43385</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>43395</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>43395</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>43402</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>43402</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>43402</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>43406</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>43411</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>43412</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>43414</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>43423</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>43423</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>43424</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>43426</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>43440</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>43441</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>43441</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43441</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>43441</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>43441</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>43445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>43445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>43445</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>43446</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>43446</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>43454</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>43454</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>43467</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>43467</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>43468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>43468</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>43473</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>43474</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>43475</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>43475</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>43481</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>43482</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>43487</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>43487</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>43488</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>43493</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>43494</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>43496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>43496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>43501</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>43506</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>43508</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>43511</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>43514</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>43515</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>43517</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>43528</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>43528</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>43530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>43530</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>43533</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>43542</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>43542</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>43543</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>43557</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>43558</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43573</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>43578</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>43579</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>43580</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>43584</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>43584</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>43588</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>43589</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>43593</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43594</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43595</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>43599</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43600</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43602</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43608</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43612</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>43612</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>43612</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>43619</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>43619</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>43621</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>43621</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>43626</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>43626</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>43634</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>43634</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>43636</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>43644</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>43647</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>43647</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>43649</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>43649</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>43651</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>43657</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>43657</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>43657</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>43661</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>43672</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>43679</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>43682</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>43683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>43689</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>43689</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>43691</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43698</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>43702</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>43703</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>43705</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>43707</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>43712</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>43714</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43719</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>43721</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>43727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>43727</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>43731</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>43740</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>43742</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>43748</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>43748</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>43756</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>43762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>43762</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>43765</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>43766</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>43767</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>43773</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43773</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43773</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43775</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>43781</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>43782</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>43783</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>43787</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>43795</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43795</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43796</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43796</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43796</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43803</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43809</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43811</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43840</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43843</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43850</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>43852</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>43858</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>43858</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>43858</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>43858</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>43860</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>43860</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>43860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43860</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>43860</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>43865</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>43866</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>43868</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43868</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43868</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43868</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43871</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43871</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43871</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43871</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43871</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43871</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43879</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>43882</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>43885</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>43886</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>43892</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>43893</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>43893</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>43910</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>43914</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>43917</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>43924</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>43930</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>43936</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>43936</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>43936</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>43937</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>43938</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>43941</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>43956</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>43956</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>43956</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>43956</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>43956</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>43957</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>43957</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>43976</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>43977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>43977</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>43980</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>43980</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>43980</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44000</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>44008</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44011</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>44015</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44026</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44029</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44034</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>44039</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44039</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44047</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44049</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44050</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44053</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44057</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44063</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44063</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44063</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44067</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44069</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44069</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44076</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44077</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44078</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44084</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44084</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44088</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44089</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>44090</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>44092</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44095</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44099</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>44100</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44104</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44105</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>44112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>44112</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>44112</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>44112</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>44112</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44113</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44120</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>44123</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44123</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>44124</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>44125</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>44130</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>44140</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>44144</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>44148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>44160</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>44161</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>44164</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>44165</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>44167</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44168</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>44168</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>44171</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44171</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>44172</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44187</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>44203</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>44203</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44207</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44215</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44216</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>44218</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>44218</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>44221</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44223</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44223</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44236</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44239</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44242</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44243</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44244</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44249</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44249</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44252</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>44258</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>44266</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44266</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44267</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44272</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>44274</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44278</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>44284</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>44284</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44294</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>44294</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>44308</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>44309</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>44309</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>44313</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44314</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44316</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44319</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>44319</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>44319</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>44320</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44322</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>44323</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>44326</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44334</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44334</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44335</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44337</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44337</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44341</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44354</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44357</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44357</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44361</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44362</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>44375</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>44375</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>44379</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>44379</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>44379</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>44379</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44382</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44383</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44392</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>44411</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44411</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>44416</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44418</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44419</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44419</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44425</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44425</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44425</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44433</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44433</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44434</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44435</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44439</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44445</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44446</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44447</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44452</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44452</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44454</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44454</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>44454</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44454</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44455</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44456</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44460</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44462</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44463</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44465</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44466</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44466</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44466</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44466</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44467</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44469</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>44469</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>44480</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>44481</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>44483</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44483</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44483</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44483</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44483</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>44484</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>44484</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44484</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44486</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44487</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44497</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44500</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>44501</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44502</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44505</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>44516</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>44517</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44517</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44525</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>44539</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>44558</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44560</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>44567</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>44567</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44568</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44575</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44578</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44585</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44587</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44587</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44587</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>44587</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>44589</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44594</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44596</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44599</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44600</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>44603</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44606</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>44608</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44608</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>44616</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>44616</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>44617</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44623</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44627</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44644</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44645</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>44650</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>44655</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>44658</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>44677</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>44677</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>44687</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>44697</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>44699</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>44699</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>44699</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>44701</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44704</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>44714</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>44720</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44725</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44728</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>44728</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44729</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44733</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44734</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44734</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>44739</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>44739</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44739</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>44742</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44743</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>44743</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44755</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>44776</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>44782</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>44782</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44789</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>44795</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>44796</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>44799</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44799</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>44799</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>44799</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>44799</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>44801</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>44801</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44802</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44804</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>44805</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44805</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>44805</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>44805</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>44805</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44811</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>44826</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44830</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>44836</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>44846</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>44851</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>44851</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>44852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>44852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>44854</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>44861</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44865</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>44868</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>44873</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>44873</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>44874</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>44882</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>44882</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>44882</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>44882</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44882</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>44886</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>44886</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>44886</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>44889</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>44889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>44890</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>44894</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44897</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>44897</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44907</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44908</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>44918</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>44918</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>44918</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>44918</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44918</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>44918</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44918</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44918</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44918</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44918</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>44918</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>44923</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>44924</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>44925</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>44930</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>44935</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>44935</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>44937</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>44937</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>44939</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>44944</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>44949</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>44949</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>44949</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>44949</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>44951</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>44952</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>44952</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>44952</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>44952</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>44952</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>44952</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>44952</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>44952</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>44953</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>44953</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>44956</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>44956</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44958</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>44958</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>44958</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>44959</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>44959</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>44960</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44960</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44964</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44965</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44967</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44970</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44972</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44974</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44974</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>44974</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>44974</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>44977</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>44977</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>44977</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>44977</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>44978</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>44978</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>44978</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>44978</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>44981</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>44981</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44982</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>44982</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>44982</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>44984</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42871,7 +42871,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>44988</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>44991</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>44991</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>44992</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>44992</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>44992</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>44993</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45000</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45000</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45000</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45000</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45000</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45001</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45005</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45005</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45007</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45007</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45007</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45007</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45008</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45009</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45009</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45014</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45020</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>45020</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45020</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45020</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>45020</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45029</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45030</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45030</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45030</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45030</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45035</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45035</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45036</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45036</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45042</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>45044</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45048</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>45049</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45056</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45057</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45062</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45062</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45062</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45062</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45062</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45063</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>45071</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45071</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45071</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45076</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>45077</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46653,7 +46653,7 @@
         <v>45078</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>45078</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>45078</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46834,7 +46834,7 @@
         <v>45078</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>45078</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45078</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>45078</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45078</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45078</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45078</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45078</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         <v>45078</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>45078</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>45082</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>45082</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45082</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>45082</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45082</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45084</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45085</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45091</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45091</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45091</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45093</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45093</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45096</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45096</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45097</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45097</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45097</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45098</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45098</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45098</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45098</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>45098</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45105</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45107</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45107</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45110</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>45111</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>45116</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>45118</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>45120</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45122</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>45123</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45123</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45128</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45134</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45139</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45139</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         <v>45141</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>45145</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>45145</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45145</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45145</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45145</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>45145</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50787,7 +50787,7 @@
         <v>45145</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45145</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50901,7 +50901,7 @@
         <v>45147</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45148</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45149</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45151</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45153</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>45154</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>45154</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51486,7 +51486,7 @@
         <v>45159</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>45160</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>45160</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45160</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>45160</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45161</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>45161</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>45161</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51947,7 +51947,7 @@
         <v>45162</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45163</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45163</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45163</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45163</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45166</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>45166</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45166</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45167</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45168</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45169</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45171</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45174</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45176</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45181</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45182</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45183</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45184</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45184</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45187</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>45187</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45187</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45187</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45187</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45187</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45187</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45188</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45188</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45188</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45191</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45194</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45194</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45194</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45195</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45195</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45196</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>45196</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45197</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45197</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45198</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45200</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45199</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45201</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45201</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>45201</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45201</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45201</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45202</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45202</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45202</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>45204</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45209</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45210</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         <v>45211</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45215</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45216</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>45216</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55796,7 +55796,7 @@
         <v>45219</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>45219</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55910,7 +55910,7 @@
         <v>45219</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>45219</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>45219</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56081,7 +56081,7 @@
         <v>45222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45222</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>45223</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45224</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45226</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45226</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45226</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45229</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56651,7 +56651,7 @@
         <v>45229</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56708,7 +56708,7 @@
         <v>45229</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45229</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>45229</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56946,7 +56946,7 @@
         <v>45229</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45230</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45232</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45232</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45232</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45232</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45232</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45232</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45232</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57464,7 +57464,7 @@
         <v>45232</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57521,7 +57521,7 @@
         <v>45235</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>45235</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>45238</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>45240</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57749,7 +57749,7 @@
         <v>45240</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57920,7 +57920,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57977,7 +57977,7 @@
         <v>45245</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45245</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45245</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58148,7 +58148,7 @@
         <v>45245</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>45246</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>45246</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45246</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>45246</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58433,7 +58433,7 @@
         <v>45247</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58490,7 +58490,7 @@
         <v>45247</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58547,7 +58547,7 @@
         <v>45250</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>45250</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>45250</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45253</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>45254</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>45257</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45257</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45257</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         <v>45259</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         <v>45260</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45260</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>45260</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         <v>45260</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>45260</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>45260</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         <v>45260</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59630,7 +59630,7 @@
         <v>45261</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         <v>45264</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         <v>45264</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59801,7 +59801,7 @@
         <v>45265</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>45266</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59972,7 +59972,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60205,7 +60205,7 @@
         <v>45267</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>45267</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45271</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>45274</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>45275</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60671,7 +60671,7 @@
         <v>45279</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45279</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60785,7 +60785,7 @@
         <v>45279</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>45279</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45279</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>45281</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61013,7 +61013,7 @@
         <v>45281</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61070,7 +61070,7 @@
         <v>45290</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45294</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61184,7 +61184,7 @@
         <v>45299</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45301</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45301</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45301</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45301</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45302</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45302</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61583,7 +61583,7 @@
         <v>45303</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61640,7 +61640,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61697,7 +61697,7 @@
         <v>45307</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45308</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45308</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45308</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>45308</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61982,7 +61982,7 @@
         <v>45308</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62039,7 +62039,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62096,7 +62096,7 @@
         <v>45314</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62153,7 +62153,7 @@
         <v>45314</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62210,7 +62210,7 @@
         <v>45314</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62267,7 +62267,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>45315</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62438,7 +62438,7 @@
         <v>45315</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62495,7 +62495,7 @@
         <v>45315</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>45315</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>45315</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>45315</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>45317</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45317</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62837,7 +62837,7 @@
         <v>45317</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>45320</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62951,7 +62951,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63008,7 +63008,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>45323</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>45324</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63293,7 +63293,7 @@
         <v>45327</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>45327</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63407,7 +63407,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45331</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63578,7 +63578,7 @@
         <v>45331</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>45333</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63685,14 +63685,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5706-2024</t>
+          <t>A 5707-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63705,7 +63705,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5707-2024</t>
+          <t>A 5706-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63762,7 +63762,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -63806,7 +63806,7 @@
         <v>45337</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>45337</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63920,7 +63920,7 @@
         <v>45341</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63977,7 +63977,7 @@
         <v>45341</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64034,7 +64034,7 @@
         <v>45341</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64091,7 +64091,7 @@
         <v>45348</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64148,7 +64148,7 @@
         <v>45348</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64205,7 +64205,7 @@
         <v>45348</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64262,7 +64262,7 @@
         <v>45348</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64324,7 +64324,7 @@
         <v>45349</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -569,7 +569,7 @@
         <v>43345</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         <v>44826</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44872</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44575</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>44575</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44088</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44484</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44974</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>44340</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44743</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44958</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45201</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>43315</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45196</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>45208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45301</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>43320</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>43353</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>43474</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43475</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43523</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>43524</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>43531</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43585</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43807</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>43809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>43879</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>43990</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44092</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44235</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44342</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44435</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44608</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44636</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44642</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44690</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44706</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44754</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44801</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44914</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44960</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44974</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45007</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45049</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45093</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45093</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45093</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45093</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45216</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45294</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45348</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>43320</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>43321</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43321</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43325</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43328</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43335</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43336</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43340</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43341</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43346</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43348</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43355</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43356</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43356</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43357</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43368</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43375</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>43376</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>43383</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>43385</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>43395</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>43395</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>43402</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>43402</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>43402</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>43406</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>43411</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>43412</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>43414</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>43423</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>43423</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>43424</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>43426</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>43440</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>43441</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>43441</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43441</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>43441</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>43441</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>43445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>43445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>43445</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>43446</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>43446</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>43454</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>43454</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>43467</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>43467</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>43468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>43468</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>43473</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>43474</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>43475</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>43475</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>43481</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>43482</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>43487</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>43487</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>43488</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>43493</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>43494</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>43496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>43496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>43501</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>43506</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>43508</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>43511</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>43514</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>43515</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>43517</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>43528</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>43528</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>43530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>43530</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>43533</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>43542</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>43542</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>43543</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>43557</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>43558</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43573</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>43578</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>43579</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>43580</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>43584</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>43584</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>43588</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>43589</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>43593</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43594</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43595</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>43599</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43600</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43602</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43608</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43612</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>43612</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>43612</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>43619</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>43619</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>43621</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>43621</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>43626</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>43626</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>43634</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>43634</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>43636</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>43644</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>43647</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>43647</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>43649</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>43649</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>43651</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>43657</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>43657</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>43657</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>43661</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>43672</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>43679</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>43682</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>43683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>43689</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>43689</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>43691</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43698</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>43702</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>43703</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>43705</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>43707</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>43712</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>43714</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43719</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>43721</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>43727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>43727</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>43731</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>43740</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>43742</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>43748</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>43748</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>43756</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>43762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>43762</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>43765</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>43766</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>43767</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>43773</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43773</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43773</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43775</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>43781</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>43782</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>43783</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>43787</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>43795</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43795</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43796</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43796</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43796</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43803</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43809</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43811</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43840</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43843</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43850</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>43852</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>43858</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>43858</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>43858</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>43858</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>43860</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>43860</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>43860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43860</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>43860</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>43865</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>43866</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>43868</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43868</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43868</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43868</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43871</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43871</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43871</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43871</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43871</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43871</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43879</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>43882</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>43885</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>43886</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>43892</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>43893</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>43893</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>43910</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>43914</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>43917</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>43924</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>43930</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>43936</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>43936</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>43936</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>43937</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>43938</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>43941</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>43956</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>43956</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>43956</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>43956</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>43956</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>43957</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>43957</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>43976</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>43977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>43977</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>43980</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>43980</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>43980</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44000</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>44008</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44011</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>44015</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44026</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44029</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44034</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>44039</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44039</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44047</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44049</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44050</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44053</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44057</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44063</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44063</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44063</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44067</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44069</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44069</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44076</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44077</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44078</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44084</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44084</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44088</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44089</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>44090</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>44092</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44095</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44099</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>44100</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44104</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44105</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>44112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>44112</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>44112</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>44112</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>44112</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44113</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44120</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>44123</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44123</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>44124</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>44125</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>44130</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>44140</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>44144</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>44148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>44160</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>44161</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>44164</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>44165</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>44167</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44168</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>44168</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>44171</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44171</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>44172</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44187</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>44203</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>44203</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44207</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44215</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44216</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>44218</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>44218</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>44221</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44223</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44223</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44236</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44239</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44242</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44243</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44244</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44249</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44249</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44252</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>44258</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>44266</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44266</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44267</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44272</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>44274</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44278</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>44284</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>44284</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44294</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>44294</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>44308</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>44309</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>44309</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>44313</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44314</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44316</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44319</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>44319</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>44319</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>44320</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44322</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>44323</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>44326</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44334</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44334</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44335</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44337</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44337</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44341</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44354</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44357</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44357</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44361</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44362</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>44375</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>44375</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>44379</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>44379</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>44379</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>44379</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44382</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44383</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44392</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>44411</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44411</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>44416</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44418</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44419</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44419</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44425</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44425</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44425</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44433</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44433</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44434</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44435</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44439</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44445</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44446</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44447</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44452</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44452</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44454</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44454</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>44454</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44454</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44455</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44456</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44460</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44462</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44463</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44465</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44466</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44466</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44466</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44466</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44467</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44469</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>44469</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>44480</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>44481</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>44483</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44483</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44483</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44483</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44483</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>44484</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>44484</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44484</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44486</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44487</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44497</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44500</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>44501</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44502</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44505</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>44516</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>44517</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44517</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44525</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>44539</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>44558</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44560</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>44567</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>44567</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44568</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44575</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44578</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44585</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44587</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44587</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44587</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>44587</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>44589</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44594</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44596</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44599</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44600</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>44603</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44606</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>44608</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44608</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>44616</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>44616</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>44617</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44623</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44627</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44644</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44645</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>44650</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>44655</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>44658</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>44677</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>44677</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>44687</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>44697</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>44699</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>44699</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>44699</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>44701</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44704</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>44714</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>44720</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44725</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44728</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>44728</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44729</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44733</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44734</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44734</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>44739</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>44739</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44739</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>44742</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44743</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>44743</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44755</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>44776</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>44782</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>44782</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44789</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>44795</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>44796</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>44799</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44799</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>44799</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>44799</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>44799</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>44801</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>44801</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44802</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44804</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>44805</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44805</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>44805</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>44805</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>44805</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44811</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>44826</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44830</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>44836</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>44846</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>44851</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>44851</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>44852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>44852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>44854</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>44861</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44865</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>44868</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>44873</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>44873</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>44874</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>44882</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>44882</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>44882</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>44882</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44882</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>44886</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>44886</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>44886</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>44889</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>44889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>44890</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>44894</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44897</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>44897</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44907</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44908</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>44918</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>44918</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>44918</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>44918</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44918</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>44918</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44918</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44918</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44918</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44918</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>44918</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>44923</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>44924</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>44925</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>44930</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>44935</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>44935</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>44937</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>44937</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>44939</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>44944</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>44949</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>44949</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>44949</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>44949</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>44951</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>44952</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>44952</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>44952</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>44952</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>44952</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>44952</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>44952</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>44952</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>44953</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>44953</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>44956</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>44956</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44958</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>44958</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>44958</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>44959</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>44959</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>44960</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44960</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44964</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44965</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44967</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44970</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44972</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44974</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44974</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>44974</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>44974</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>44977</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>44977</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>44977</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>44977</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>44978</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>44978</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>44978</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>44978</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>44981</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>44981</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44982</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>44982</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>44982</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>44984</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42871,7 +42871,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>44988</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>44991</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>44991</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>44992</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>44992</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>44992</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>44993</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45000</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45000</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45000</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45000</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45000</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45001</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45005</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45005</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45007</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45007</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45007</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45007</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45008</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45009</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45009</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45014</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45020</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>45020</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45020</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45020</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>45020</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45029</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45030</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45030</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45030</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45030</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45035</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45035</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45036</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45036</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45042</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>45044</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45048</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>45049</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45056</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45057</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45062</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45062</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45062</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45062</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45062</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45063</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>45071</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45071</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45071</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45076</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>45077</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46653,7 +46653,7 @@
         <v>45078</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>45078</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>45078</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46834,7 +46834,7 @@
         <v>45078</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>45078</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45078</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>45078</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45078</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45078</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45078</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45078</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         <v>45078</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>45078</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>45082</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>45082</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45082</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>45082</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45082</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45084</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45085</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45091</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45091</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45091</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45093</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45093</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45096</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45096</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45097</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45097</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45097</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45098</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45098</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45098</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45098</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>45098</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45105</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45107</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45107</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45110</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>45111</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>45116</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>45118</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>45120</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45122</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>45123</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45123</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45128</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45134</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45139</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45139</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         <v>45141</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>45145</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>45145</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45145</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45145</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45145</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>45145</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50787,7 +50787,7 @@
         <v>45145</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45145</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50901,7 +50901,7 @@
         <v>45147</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45148</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45149</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45151</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45153</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>45154</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>45154</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51486,7 +51486,7 @@
         <v>45159</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>45160</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>45160</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45160</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>45160</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45161</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>45161</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>45161</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51947,7 +51947,7 @@
         <v>45162</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45163</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45163</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45163</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45163</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45166</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>45166</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45166</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45167</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45168</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45169</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45171</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45174</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45176</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45181</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45182</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45183</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45184</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45184</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45187</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>45187</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45187</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45187</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45187</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45187</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45187</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45188</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45188</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45188</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45191</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45194</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45194</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45194</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45195</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45195</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45196</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>45196</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45197</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45197</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45198</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45200</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45199</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45201</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45201</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>45201</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45201</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45201</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45202</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45202</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45202</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>45204</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45209</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45210</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         <v>45211</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45215</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45216</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>45216</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55796,7 +55796,7 @@
         <v>45219</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>45219</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55910,7 +55910,7 @@
         <v>45219</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>45219</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>45219</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56081,7 +56081,7 @@
         <v>45222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45222</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>45223</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45224</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45226</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45226</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45226</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45229</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56651,7 +56651,7 @@
         <v>45229</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56708,7 +56708,7 @@
         <v>45229</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45229</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>45229</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56946,7 +56946,7 @@
         <v>45229</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45230</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45232</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45232</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45232</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45232</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45232</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45232</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45232</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57464,7 +57464,7 @@
         <v>45232</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57521,7 +57521,7 @@
         <v>45235</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>45235</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>45238</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>45240</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57749,7 +57749,7 @@
         <v>45240</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57920,7 +57920,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57977,7 +57977,7 @@
         <v>45245</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45245</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45245</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58148,7 +58148,7 @@
         <v>45245</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>45246</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>45246</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45246</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>45246</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58433,7 +58433,7 @@
         <v>45247</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58490,7 +58490,7 @@
         <v>45247</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58547,7 +58547,7 @@
         <v>45250</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>45250</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>45250</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45253</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>45254</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>45257</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45257</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45257</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         <v>45259</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         <v>45260</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45260</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>45260</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         <v>45260</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>45260</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>45260</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         <v>45260</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59630,7 +59630,7 @@
         <v>45261</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         <v>45264</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         <v>45264</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59801,7 +59801,7 @@
         <v>45265</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>45266</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59972,7 +59972,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60205,7 +60205,7 @@
         <v>45267</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>45267</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45271</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>45274</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>45275</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60671,7 +60671,7 @@
         <v>45279</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45279</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60785,7 +60785,7 @@
         <v>45279</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>45279</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45279</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>45281</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61013,7 +61013,7 @@
         <v>45281</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61070,7 +61070,7 @@
         <v>45290</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45294</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61184,7 +61184,7 @@
         <v>45299</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45301</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45301</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45301</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45301</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45302</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45302</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61583,7 +61583,7 @@
         <v>45303</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61640,7 +61640,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61697,7 +61697,7 @@
         <v>45307</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45308</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45308</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45308</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>45308</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61982,7 +61982,7 @@
         <v>45308</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62039,7 +62039,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62096,7 +62096,7 @@
         <v>45314</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62153,7 +62153,7 @@
         <v>45314</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62210,7 +62210,7 @@
         <v>45314</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62267,7 +62267,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>45315</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62438,7 +62438,7 @@
         <v>45315</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62495,7 +62495,7 @@
         <v>45315</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>45315</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>45315</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>45315</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>45317</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45317</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62837,7 +62837,7 @@
         <v>45317</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>45320</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62951,7 +62951,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63008,7 +63008,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>45323</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>45324</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63286,14 +63286,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 4433-2024</t>
+          <t>A 4432-2024</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63306,7 +63306,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -63343,14 +63343,14 @@
     <row r="1063" ht="15" customHeight="1">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>A 4432-2024</t>
+          <t>A 4433-2024</t>
         </is>
       </c>
       <c r="B1063" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63363,7 +63363,7 @@
         </is>
       </c>
       <c r="G1063" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>
@@ -63407,7 +63407,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45331</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63578,7 +63578,7 @@
         <v>45331</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>45333</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63685,14 +63685,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5707-2024</t>
+          <t>A 5706-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63705,7 +63705,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5706-2024</t>
+          <t>A 5707-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63762,7 +63762,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -63799,14 +63799,14 @@
     <row r="1071" ht="15" customHeight="1">
       <c r="A1071" t="inlineStr">
         <is>
-          <t>A 6159-2024</t>
+          <t>A 6156-2024</t>
         </is>
       </c>
       <c r="B1071" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63819,7 +63819,7 @@
         </is>
       </c>
       <c r="G1071" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="H1071" t="n">
         <v>0</v>
@@ -63856,14 +63856,14 @@
     <row r="1072" ht="15" customHeight="1">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>A 6156-2024</t>
+          <t>A 6159-2024</t>
         </is>
       </c>
       <c r="B1072" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63876,7 +63876,7 @@
         </is>
       </c>
       <c r="G1072" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="H1072" t="n">
         <v>0</v>
@@ -63920,7 +63920,7 @@
         <v>45341</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63977,7 +63977,7 @@
         <v>45341</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64034,7 +64034,7 @@
         <v>45341</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64091,7 +64091,7 @@
         <v>45348</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64148,7 +64148,7 @@
         <v>45348</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64205,7 +64205,7 @@
         <v>45348</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64262,7 +64262,7 @@
         <v>45348</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64324,7 +64324,7 @@
         <v>45349</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64379,14 +64379,14 @@
     <row r="1081" ht="15" customHeight="1">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>A 8088-2024</t>
+          <t>A 8064-2024</t>
         </is>
       </c>
       <c r="B1081" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64399,7 +64399,7 @@
         </is>
       </c>
       <c r="G1081" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="H1081" t="n">
         <v>0</v>
@@ -64436,14 +64436,14 @@
     <row r="1082" ht="15" customHeight="1">
       <c r="A1082" t="inlineStr">
         <is>
-          <t>A 8092-2024</t>
+          <t>A 8088-2024</t>
         </is>
       </c>
       <c r="B1082" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -64456,7 +64456,7 @@
         </is>
       </c>
       <c r="G1082" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H1082" t="n">
         <v>0</v>
@@ -64493,14 +64493,14 @@
     <row r="1083" ht="15" customHeight="1">
       <c r="A1083" t="inlineStr">
         <is>
-          <t>A 8064-2024</t>
+          <t>A 8092-2024</t>
         </is>
       </c>
       <c r="B1083" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -64513,7 +64513,7 @@
         </is>
       </c>
       <c r="G1083" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="H1083" t="n">
         <v>0</v>
@@ -64557,7 +64557,7 @@
         <v>45352</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -569,7 +569,7 @@
         <v>43345</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         <v>44826</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44872</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44575</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>44575</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44088</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44484</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44974</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>44340</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44743</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44958</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45201</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>43315</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45196</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>45208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45301</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>43320</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>43353</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>43474</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43475</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43523</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>43524</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>43531</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43585</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43807</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>43809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>43879</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>43990</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44092</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44235</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44342</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44435</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44608</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44636</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44642</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44690</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44706</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44754</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44801</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44914</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44960</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44974</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45007</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45049</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45093</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45093</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45093</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45093</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45216</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45294</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45348</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>43320</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>43321</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43321</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43325</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43328</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43335</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43336</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43340</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43341</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43346</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43348</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43355</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43356</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43356</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43357</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43368</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43375</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>43376</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>43383</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>43385</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>43395</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>43395</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>43402</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>43402</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>43402</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>43406</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>43411</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>43412</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>43414</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>43423</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>43423</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>43424</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>43426</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>43440</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>43441</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>43441</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43441</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>43441</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>43441</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>43445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>43445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>43445</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>43446</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>43446</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>43454</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>43454</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>43467</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>43467</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>43468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>43468</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>43473</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>43474</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>43475</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>43475</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>43481</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>43482</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>43487</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>43487</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>43488</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>43493</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>43494</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>43496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>43496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>43501</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>43506</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>43508</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>43511</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>43514</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>43515</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>43517</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>43528</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>43528</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>43530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>43530</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>43533</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>43542</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>43542</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>43543</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>43557</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>43558</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43573</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>43578</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>43579</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>43580</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>43584</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>43584</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>43588</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>43589</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>43593</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43594</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43595</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>43599</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43600</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43602</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43608</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43612</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>43612</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>43612</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>43619</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>43619</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>43621</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>43621</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>43626</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>43626</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>43634</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>43634</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>43636</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>43644</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>43647</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>43647</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>43649</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>43649</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>43651</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>43657</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>43657</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>43657</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>43661</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>43672</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>43679</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>43682</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>43683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>43689</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>43689</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>43691</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43698</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>43702</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>43703</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>43705</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>43707</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>43712</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>43714</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43719</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>43721</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>43727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>43727</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>43731</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>43740</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>43742</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>43748</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>43748</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>43756</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>43762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>43762</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>43765</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>43766</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>43767</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>43773</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43773</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43773</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43775</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>43781</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>43782</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>43783</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>43787</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>43795</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43795</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43796</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43796</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43796</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43803</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43809</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43811</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43840</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43843</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43850</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>43852</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>43858</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>43858</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>43858</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>43858</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>43860</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>43860</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>43860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43860</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>43860</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>43865</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>43866</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>43868</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43868</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43868</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43868</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43871</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43871</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43871</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43871</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43871</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43871</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43879</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>43882</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>43885</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>43886</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>43892</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>43893</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>43893</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>43910</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>43914</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>43917</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>43924</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>43930</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>43936</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>43936</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>43936</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>43937</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>43938</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>43941</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>43956</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>43956</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>43956</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>43956</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>43956</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>43957</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>43957</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>43976</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>43977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>43977</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>43980</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>43980</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>43980</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44000</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>44008</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44011</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>44015</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44026</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44029</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44034</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>44039</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44039</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44047</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44049</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44050</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44053</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44057</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44063</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44063</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44063</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44067</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44069</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44069</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44076</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44077</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44078</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44084</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44084</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44088</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44089</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>44090</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>44092</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44095</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44099</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>44100</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44104</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44105</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>44112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>44112</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>44112</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>44112</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>44112</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44113</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44120</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>44123</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44123</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>44124</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>44125</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>44130</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>44140</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>44144</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>44148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>44160</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>44161</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>44164</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>44165</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>44167</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44168</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>44168</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>44171</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44171</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>44172</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44187</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>44203</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>44203</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44207</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44215</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44216</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>44218</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>44218</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>44221</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44223</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44223</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44236</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44239</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44242</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44243</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44244</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44249</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44249</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44252</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>44258</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>44266</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44266</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44267</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44272</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>44274</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44278</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>44284</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>44284</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44294</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>44294</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>44308</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>44309</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>44309</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>44313</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44314</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44316</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44319</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>44319</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>44319</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>44320</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44322</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>44323</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>44326</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44334</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44334</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44335</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44337</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44337</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44341</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44354</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44357</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44357</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44361</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44362</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>44375</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>44375</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>44379</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>44379</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>44379</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>44379</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44382</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44383</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44392</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>44411</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44411</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>44416</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44418</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44419</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44419</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44425</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44425</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44425</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44433</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44433</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44434</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44435</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44439</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44445</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44446</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44447</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44452</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44452</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44454</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44454</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>44454</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44454</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44455</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44456</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44460</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44462</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44463</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44465</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44466</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44466</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44466</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44466</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44467</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44469</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>44469</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>44480</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>44481</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>44483</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44483</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44483</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44483</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44483</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>44484</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>44484</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44484</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44486</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44487</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44497</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44500</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>44501</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44502</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44505</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>44516</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>44517</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44517</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44525</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>44539</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>44558</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44560</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>44567</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>44567</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44568</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44575</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44578</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44585</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44587</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44587</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44587</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>44587</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>44589</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44594</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44596</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44599</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44600</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>44603</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44606</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>44608</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44608</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>44616</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>44616</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>44617</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44623</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44627</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44644</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44645</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>44650</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>44655</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>44658</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>44677</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>44677</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>44687</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>44697</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>44699</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>44699</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>44699</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>44701</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44704</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>44714</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>44720</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44725</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44728</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>44728</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44729</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44733</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44734</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44734</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>44739</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>44739</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44739</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>44742</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44743</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>44743</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44755</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>44776</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>44782</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>44782</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44789</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>44795</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>44796</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>44799</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44799</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>44799</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>44799</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>44799</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>44801</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>44801</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44802</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44804</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>44805</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44805</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>44805</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>44805</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>44805</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44811</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>44826</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44830</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>44836</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>44846</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>44851</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>44851</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>44852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>44852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>44854</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>44861</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44865</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>44868</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>44873</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>44873</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>44874</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>44882</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>44882</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>44882</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>44882</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44882</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>44886</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>44886</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>44886</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>44889</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>44889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>44890</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>44894</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44897</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>44897</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44907</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44908</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>44918</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>44918</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>44918</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>44918</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44918</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>44918</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44918</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44918</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44918</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44918</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>44918</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>44923</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>44924</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>44925</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>44930</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>44935</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>44935</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>44937</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>44937</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>44939</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>44944</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>44949</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>44949</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>44949</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>44949</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>44951</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>44952</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>44952</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>44952</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>44952</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>44952</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>44952</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>44952</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>44952</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>44953</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>44953</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>44956</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>44956</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44958</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>44958</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>44958</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>44959</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>44959</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>44960</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44960</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44964</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44965</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44967</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44970</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44972</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44974</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44974</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>44974</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>44974</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>44977</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>44977</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>44977</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>44977</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>44978</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>44978</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>44978</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>44978</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>44981</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>44981</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44982</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>44982</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>44982</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>44984</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42871,7 +42871,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>44988</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>44991</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>44991</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>44992</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>44992</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>44992</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>44993</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45000</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45000</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45000</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45000</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45000</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45001</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45005</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45005</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45007</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45007</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45007</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45007</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45008</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45009</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45009</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45014</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45020</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>45020</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45020</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45020</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>45020</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45029</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45030</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45030</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45030</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45030</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45035</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45035</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45036</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45036</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45042</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>45044</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45048</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>45049</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45056</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45057</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45062</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45062</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45062</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45062</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45062</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45063</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>45071</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45071</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45071</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45076</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>45077</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46653,7 +46653,7 @@
         <v>45078</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>45078</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>45078</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46834,7 +46834,7 @@
         <v>45078</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>45078</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45078</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>45078</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45078</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45078</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45078</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45078</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         <v>45078</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>45078</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>45082</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>45082</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45082</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>45082</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45082</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45084</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45085</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45091</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45091</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45091</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45093</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45093</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45096</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45096</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45097</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45097</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45097</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45098</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45098</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45098</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45098</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>45098</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45105</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45107</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45107</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45110</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>45111</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>45116</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>45118</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>45120</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45122</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>45123</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45123</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45128</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45134</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45139</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45139</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         <v>45141</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>45145</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>45145</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45145</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45145</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45145</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>45145</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50787,7 +50787,7 @@
         <v>45145</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45145</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50901,7 +50901,7 @@
         <v>45147</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45148</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45149</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45151</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45153</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>45154</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>45154</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51486,7 +51486,7 @@
         <v>45159</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>45160</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>45160</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45160</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>45160</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45161</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>45161</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>45161</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51947,7 +51947,7 @@
         <v>45162</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45163</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45163</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45163</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45163</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45166</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>45166</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45166</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45167</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45168</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45169</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45171</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45174</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45176</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45181</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45182</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45183</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45184</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45184</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45187</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>45187</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45187</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45187</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45187</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45187</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45187</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45188</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45188</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45188</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45191</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45194</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45194</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45194</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45195</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45195</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45196</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>45196</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45197</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45197</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45198</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45200</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45199</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45201</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45201</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>45201</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45201</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45201</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45202</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45202</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45202</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>45204</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45209</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45210</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         <v>45211</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45215</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45216</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>45216</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55796,7 +55796,7 @@
         <v>45219</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>45219</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55910,7 +55910,7 @@
         <v>45219</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>45219</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>45219</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56081,7 +56081,7 @@
         <v>45222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45222</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>45223</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45224</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45226</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45226</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45226</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45229</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56651,7 +56651,7 @@
         <v>45229</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56708,7 +56708,7 @@
         <v>45229</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45229</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>45229</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56946,7 +56946,7 @@
         <v>45229</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45230</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45232</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45232</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45232</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45232</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45232</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45232</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45232</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57464,7 +57464,7 @@
         <v>45232</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57521,7 +57521,7 @@
         <v>45235</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>45235</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>45238</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>45240</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57749,7 +57749,7 @@
         <v>45240</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57920,7 +57920,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57977,7 +57977,7 @@
         <v>45245</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45245</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45245</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58148,7 +58148,7 @@
         <v>45245</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>45246</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>45246</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45246</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>45246</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58433,7 +58433,7 @@
         <v>45247</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58490,7 +58490,7 @@
         <v>45247</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58547,7 +58547,7 @@
         <v>45250</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>45250</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>45250</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45253</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>45254</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>45257</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45257</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45257</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         <v>45259</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         <v>45260</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45260</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>45260</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         <v>45260</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>45260</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>45260</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         <v>45260</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59630,7 +59630,7 @@
         <v>45261</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         <v>45264</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         <v>45264</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59801,7 +59801,7 @@
         <v>45265</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>45266</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59972,7 +59972,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60205,7 +60205,7 @@
         <v>45267</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>45267</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45271</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>45274</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>45275</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60671,7 +60671,7 @@
         <v>45279</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45279</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60785,7 +60785,7 @@
         <v>45279</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>45279</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45279</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>45281</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61013,7 +61013,7 @@
         <v>45281</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61070,7 +61070,7 @@
         <v>45290</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45294</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61184,7 +61184,7 @@
         <v>45299</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45301</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45301</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45301</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45301</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45302</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45302</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61583,7 +61583,7 @@
         <v>45303</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61640,7 +61640,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61697,7 +61697,7 @@
         <v>45307</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45308</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45308</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45308</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>45308</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61982,7 +61982,7 @@
         <v>45308</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62039,7 +62039,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62096,7 +62096,7 @@
         <v>45314</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62153,7 +62153,7 @@
         <v>45314</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62210,7 +62210,7 @@
         <v>45314</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62267,7 +62267,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>45315</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62438,7 +62438,7 @@
         <v>45315</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62495,7 +62495,7 @@
         <v>45315</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>45315</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>45315</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>45315</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>45317</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45317</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62837,7 +62837,7 @@
         <v>45317</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>45320</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62951,7 +62951,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63008,7 +63008,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>45323</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>45324</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63286,14 +63286,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 4432-2024</t>
+          <t>A 4433-2024</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63306,7 +63306,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -63343,14 +63343,14 @@
     <row r="1063" ht="15" customHeight="1">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>A 4433-2024</t>
+          <t>A 4432-2024</t>
         </is>
       </c>
       <c r="B1063" s="1" t="n">
         <v>45327</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63363,7 +63363,7 @@
         </is>
       </c>
       <c r="G1063" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>
@@ -63407,7 +63407,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45331</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63578,7 +63578,7 @@
         <v>45331</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>45333</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63692,7 +63692,7 @@
         <v>45334</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63749,7 +63749,7 @@
         <v>45334</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>45337</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>45337</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63920,7 +63920,7 @@
         <v>45341</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63977,7 +63977,7 @@
         <v>45341</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64034,7 +64034,7 @@
         <v>45341</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64084,14 +64084,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 7629-2024</t>
+          <t>A 7631-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64104,7 +64104,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -64141,14 +64141,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 7645-2024</t>
+          <t>A 7629-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64161,7 +64161,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>
@@ -64198,14 +64198,14 @@
     <row r="1078" ht="15" customHeight="1">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>A 7631-2024</t>
+          <t>A 7659-2024</t>
         </is>
       </c>
       <c r="B1078" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64217,8 +64217,13 @@
           <t>KINDA</t>
         </is>
       </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="G1078" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="H1078" t="n">
         <v>0</v>
@@ -64255,14 +64260,14 @@
     <row r="1079" ht="15" customHeight="1">
       <c r="A1079" t="inlineStr">
         <is>
-          <t>A 7659-2024</t>
+          <t>A 7645-2024</t>
         </is>
       </c>
       <c r="B1079" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64274,13 +64279,8 @@
           <t>KINDA</t>
         </is>
       </c>
-      <c r="F1079" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="G1079" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="H1079" t="n">
         <v>0</v>
@@ -64324,7 +64324,7 @@
         <v>45349</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64386,7 +64386,7 @@
         <v>45351</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64443,7 +64443,7 @@
         <v>45351</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -64500,7 +64500,7 @@
         <v>45351</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -64557,7 +64557,7 @@
         <v>45352</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45354</v>
+        <v>45355</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -569,7 +569,7 @@
         <v>43345</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         <v>44826</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>44872</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>44575</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>44575</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>44939</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44088</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>44484</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44974</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>44340</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44743</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>44958</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>44972</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45201</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>43315</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>44478</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>45196</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>45208</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45301</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>43320</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>43353</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>43474</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>43475</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>43523</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>43524</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>43531</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>43585</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>43807</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>43809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>43879</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>43990</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>44092</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>44235</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44342</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>44418</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44419</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>44435</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44483</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44608</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>44636</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44642</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44690</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>44706</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44754</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44801</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>44914</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>44960</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>44974</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45007</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45049</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45093</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45093</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45093</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>45093</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>45216</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>45238</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>45294</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45348</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>43320</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>43321</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>43321</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>43325</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>43328</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>43335</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>43336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>43336</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>43340</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>43341</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>43346</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>43348</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43355</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>43356</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>43356</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>43357</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>43368</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>43375</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>43376</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>43383</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>43385</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>43388</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>43395</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>43395</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>43402</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>43402</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>43402</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>43402</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>43402</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>43406</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>43411</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>43412</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>43414</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>43419</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>43419</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>43419</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>43423</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>43423</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>43424</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>43426</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>43438</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>43440</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>43441</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>43441</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>43441</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>43441</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>43441</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>43445</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>43445</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8701,7 +8701,7 @@
         <v>43445</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>43446</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>43446</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>43454</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>43454</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>43467</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>43467</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>43468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>43468</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>43473</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>43474</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>43475</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         <v>43475</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>43481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>43481</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>43482</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>43487</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>43487</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>43487</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>43488</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>43493</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>43494</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>43496</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>43496</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>43501</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>43506</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>43508</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>43511</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>43514</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>43515</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>43517</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>43528</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>43528</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>43530</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>43530</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>43533</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>43542</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>43542</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>43543</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>43557</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>43558</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>43563</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>43563</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>43573</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>43578</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>43579</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>43579</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>43580</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>43584</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>43584</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>43584</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>43588</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>43589</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>43593</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>43594</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>43595</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>43599</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>43600</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>43602</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>43608</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>43612</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>43612</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>43612</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>43619</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>43619</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>43621</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>43621</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>43626</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>43626</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>43634</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>43634</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>43636</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>43644</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>43647</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>43647</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>43649</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>43649</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>43651</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>43657</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>43657</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>43657</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>43661</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13395,7 +13395,7 @@
         <v>43672</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>43679</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>43682</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>43683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>43685</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>43689</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>43689</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>43689</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>43691</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>43696</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>43696</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>43696</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>43698</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>43698</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>43698</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>43699</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>43702</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>43703</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>43705</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>43706</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>43707</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>43707</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>43710</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>43711</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>43712</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>43714</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>43719</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>43721</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>43725</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>43727</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>43727</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>43731</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>43735</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>43740</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>43742</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>43748</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>43748</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>43756</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>43762</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>43762</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>43765</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>43766</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>43767</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>43767</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>43767</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>43767</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>43773</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>43773</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>43773</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>43775</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>43781</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>43782</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>43783</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>43787</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>43795</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>43795</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>43796</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>43796</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>43796</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17058,7 +17058,7 @@
         <v>43803</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>43809</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43811</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43840</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43843</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43843</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43850</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>43852</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>43858</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>43858</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>43858</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>43858</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>43860</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>43860</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>43860</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43860</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>43860</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>43865</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>43866</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>43868</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43868</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43868</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43868</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43871</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43871</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43871</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43871</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43871</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43871</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43879</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>43882</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>43885</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>43886</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>43892</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>43893</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>43893</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>43910</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>43914</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>43915</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>43917</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>43923</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>43924</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>43930</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>43936</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>43936</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>43936</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19720,7 +19720,7 @@
         <v>43937</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>43938</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>43941</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>43956</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>43956</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>43956</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>43956</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>43956</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>43957</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>43957</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>43976</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>43977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>43977</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>43980</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>43980</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>43980</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>43990</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44000</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>44008</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>44011</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>44015</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44026</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44029</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>44034</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>44039</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>44039</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44047</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>44049</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>44050</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>44053</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>44057</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44063</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         <v>44063</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>44063</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44067</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44068</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44069</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44069</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44076</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44077</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         <v>44078</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>44084</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>44084</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>44088</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44089</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>44090</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>44092</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>44095</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>44099</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>44100</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44104</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>44105</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>44112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>44112</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>44112</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>44112</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>44112</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>44113</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>44120</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>44123</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>44123</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>44124</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>44125</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>44130</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>44140</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>44144</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>44148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23671,7 +23671,7 @@
         <v>44160</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23728,7 +23728,7 @@
         <v>44161</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>44164</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>44165</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>44167</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>44168</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24013,7 +24013,7 @@
         <v>44168</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>44171</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44171</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>44172</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>44187</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>44203</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>44203</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>44203</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44207</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44215</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44216</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>44218</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>44218</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>44221</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44223</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44223</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44236</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44239</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44242</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44243</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>44244</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44249</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44249</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>44252</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>44258</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>44266</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>44266</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>44267</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>44272</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>44274</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44278</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>44284</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>44284</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44294</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>44294</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26013,7 +26013,7 @@
         <v>44308</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>44309</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>44309</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>44313</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>44314</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>44316</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44319</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>44319</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>44319</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>44320</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>44322</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>44323</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>44326</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44334</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44334</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44335</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>44337</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>44337</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>44341</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>44354</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>44357</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44357</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>44361</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44362</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>44364</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>44375</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>44375</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>44379</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>44379</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>44379</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>44379</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>44379</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>44382</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>44383</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44392</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>44411</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44411</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>44416</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44418</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44419</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44419</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44425</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>44425</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>44425</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>44433</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44433</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44434</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44435</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44439</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44442</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44442</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44445</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44446</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44446</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44447</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44452</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44452</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44454</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44454</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>44454</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44454</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>44455</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44456</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44460</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>44462</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44463</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44463</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44465</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44466</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>44466</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>44466</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44466</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>44467</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>44469</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>44469</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>44480</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>44481</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>44483</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>44483</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30556,7 +30556,7 @@
         <v>44483</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44483</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30670,7 +30670,7 @@
         <v>44483</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30727,7 +30727,7 @@
         <v>44484</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>44484</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30841,7 +30841,7 @@
         <v>44484</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>44486</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30955,7 +30955,7 @@
         <v>44487</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31012,7 +31012,7 @@
         <v>44497</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>44500</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>44501</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44502</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44505</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>44516</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31354,7 +31354,7 @@
         <v>44517</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44517</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44525</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         <v>44539</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>44558</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31639,7 +31639,7 @@
         <v>44560</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31696,7 +31696,7 @@
         <v>44567</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>44567</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44568</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44575</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31924,7 +31924,7 @@
         <v>44578</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31981,7 +31981,7 @@
         <v>44585</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44587</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44587</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>44587</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>44587</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32266,7 +32266,7 @@
         <v>44589</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32323,7 +32323,7 @@
         <v>44594</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>44596</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32437,7 +32437,7 @@
         <v>44599</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44600</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>44603</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44606</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>44608</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>44608</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>44616</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32846,7 +32846,7 @@
         <v>44616</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32903,7 +32903,7 @@
         <v>44617</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32960,7 +32960,7 @@
         <v>44623</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>44627</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>44644</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>44645</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>44650</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>44655</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33307,7 +33307,7 @@
         <v>44657</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>44658</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
         <v>44677</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>44677</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>44687</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>44697</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>44699</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>44699</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>44699</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>44701</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>44704</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>44714</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33991,7 +33991,7 @@
         <v>44720</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34048,7 +34048,7 @@
         <v>44721</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>44725</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44728</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>44728</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>44729</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>44732</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34390,7 +34390,7 @@
         <v>44733</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>44733</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>44734</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34561,7 +34561,7 @@
         <v>44734</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>44739</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34675,7 +34675,7 @@
         <v>44739</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>44739</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>44742</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>44743</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>44743</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44755</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>44776</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>44782</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35131,7 +35131,7 @@
         <v>44782</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>44789</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>44795</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>44796</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>44799</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         <v>44799</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>44799</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>44799</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>44799</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35644,7 +35644,7 @@
         <v>44801</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>44801</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44802</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44804</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>44805</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35934,7 +35934,7 @@
         <v>44805</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>44805</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>44805</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>44805</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44811</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36219,7 +36219,7 @@
         <v>44818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36276,7 +36276,7 @@
         <v>44826</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>44830</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>44836</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44837</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>44839</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36561,7 +36561,7 @@
         <v>44839</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36618,7 +36618,7 @@
         <v>44839</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>44846</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>44851</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36789,7 +36789,7 @@
         <v>44851</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36846,7 +36846,7 @@
         <v>44851</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>44852</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44852</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>44852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>44854</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>44860</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>44861</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44865</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>44868</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>44868</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>44873</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>44873</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>44874</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>44882</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37644,7 +37644,7 @@
         <v>44882</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>44882</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>44882</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44882</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>44886</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>44886</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>44886</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38043,7 +38043,7 @@
         <v>44889</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>44889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38157,7 +38157,7 @@
         <v>44890</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>44894</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44897</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>44897</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44907</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44908</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>44918</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>44918</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
         <v>44918</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         <v>44918</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44918</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>44918</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44918</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44918</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>44918</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39027,7 +39027,7 @@
         <v>44918</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39084,7 +39084,7 @@
         <v>44918</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39141,7 +39141,7 @@
         <v>44923</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39203,7 +39203,7 @@
         <v>44924</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>44925</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>44930</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>44935</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>44935</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>44937</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>44937</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>44937</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39659,7 +39659,7 @@
         <v>44939</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39716,7 +39716,7 @@
         <v>44944</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39773,7 +39773,7 @@
         <v>44949</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>44949</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39887,7 +39887,7 @@
         <v>44949</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>44949</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>44951</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>44952</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>44952</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>44952</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>44952</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>44952</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>44952</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>44952</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>44952</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>44952</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>44952</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>44953</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>44953</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>44956</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>44956</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>44958</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>44958</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>44958</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>44959</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>44959</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>44960</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>44960</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>44963</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41322,7 +41322,7 @@
         <v>44963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>44964</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44965</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>44967</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44970</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44970</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>44970</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>44972</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>44974</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>44974</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>44974</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>44974</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>44974</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>44977</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>44977</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42187,7 +42187,7 @@
         <v>44977</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42244,7 +42244,7 @@
         <v>44977</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         <v>44978</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>44978</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42415,7 +42415,7 @@
         <v>44978</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>44978</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42529,7 +42529,7 @@
         <v>44981</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>44981</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44982</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>44982</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42757,7 +42757,7 @@
         <v>44982</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>44984</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42871,7 +42871,7 @@
         <v>44985</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>44988</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>44991</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>44991</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>44992</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>44992</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>44992</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>44992</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>44993</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>44998</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45000</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45000</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43555,7 +43555,7 @@
         <v>45000</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45000</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>45000</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>45000</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45000</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45000</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45000</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45001</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45005</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45005</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45007</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45007</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>45007</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45007</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45008</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45009</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45009</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45014</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45020</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>45020</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45020</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45020</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>45020</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45029</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45030</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>45030</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45030</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>45030</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45035</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45035</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45036</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>45036</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45037</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45042</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45042</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>45044</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45048</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>45049</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45056</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45057</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45062</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45062</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45062</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>45062</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45062</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>45062</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45063</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>45071</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>45071</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45071</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45071</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45076</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>45077</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46653,7 +46653,7 @@
         <v>45078</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>45078</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>45078</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46834,7 +46834,7 @@
         <v>45078</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>45078</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45078</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>45078</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>45078</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45078</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45078</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45078</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         <v>45078</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>45078</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45078</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>45082</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>45082</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>45082</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45082</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>45082</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>45082</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45084</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45085</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>45086</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>45089</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>45089</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45091</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45091</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45091</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45093</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45093</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45096</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45096</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45097</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45097</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45097</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45098</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45098</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45098</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45098</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>45098</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45105</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45107</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45107</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45110</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>45111</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45111</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>45111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>45111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>45112</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45114</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>45116</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>45118</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49761,7 +49761,7 @@
         <v>45118</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45118</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>45119</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>45120</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45122</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>45123</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>45123</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45128</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45134</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45139</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45139</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50388,7 +50388,7 @@
         <v>45141</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50445,7 +50445,7 @@
         <v>45145</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>45145</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45145</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45145</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45145</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50730,7 +50730,7 @@
         <v>45145</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50787,7 +50787,7 @@
         <v>45145</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45145</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50901,7 +50901,7 @@
         <v>45147</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50958,7 +50958,7 @@
         <v>45148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45148</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45149</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45149</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51186,7 +51186,7 @@
         <v>45151</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51243,7 +51243,7 @@
         <v>45153</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45154</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>45154</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>45154</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51486,7 +51486,7 @@
         <v>45159</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>45160</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51600,7 +51600,7 @@
         <v>45160</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45160</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51719,7 +51719,7 @@
         <v>45160</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51776,7 +51776,7 @@
         <v>45161</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51833,7 +51833,7 @@
         <v>45161</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>45161</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51947,7 +51947,7 @@
         <v>45162</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52009,7 +52009,7 @@
         <v>45163</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52066,7 +52066,7 @@
         <v>45163</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>45163</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>45163</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52237,7 +52237,7 @@
         <v>45166</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>45166</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45166</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>45167</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>45167</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52522,7 +52522,7 @@
         <v>45168</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52584,7 +52584,7 @@
         <v>45169</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45171</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -52703,7 +52703,7 @@
         <v>45174</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45174</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>45174</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
         <v>45174</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>45175</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45175</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53045,7 +53045,7 @@
         <v>45176</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53102,7 +53102,7 @@
         <v>45176</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53159,7 +53159,7 @@
         <v>45176</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53216,7 +53216,7 @@
         <v>45181</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>45182</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53330,7 +53330,7 @@
         <v>45183</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53387,7 +53387,7 @@
         <v>45184</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53444,7 +53444,7 @@
         <v>45184</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45187</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>45187</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45187</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45187</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>45187</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53791,7 +53791,7 @@
         <v>45187</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53848,7 +53848,7 @@
         <v>45187</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53905,7 +53905,7 @@
         <v>45187</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53962,7 +53962,7 @@
         <v>45188</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54019,7 +54019,7 @@
         <v>45188</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54076,7 +54076,7 @@
         <v>45188</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         <v>45191</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54190,7 +54190,7 @@
         <v>45194</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54247,7 +54247,7 @@
         <v>45194</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45194</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45195</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45195</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54475,7 +54475,7 @@
         <v>45196</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>45196</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45197</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>45197</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>45198</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54822,7 +54822,7 @@
         <v>45200</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54879,7 +54879,7 @@
         <v>45199</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45201</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54993,7 +54993,7 @@
         <v>45201</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55050,7 +55050,7 @@
         <v>45201</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55107,7 +55107,7 @@
         <v>45201</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55164,7 +55164,7 @@
         <v>45201</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45202</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45202</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>45202</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>45204</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55449,7 +55449,7 @@
         <v>45209</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45210</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55563,7 +55563,7 @@
         <v>45211</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55625,7 +55625,7 @@
         <v>45215</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -55682,7 +55682,7 @@
         <v>45216</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>45216</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55796,7 +55796,7 @@
         <v>45219</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55853,7 +55853,7 @@
         <v>45219</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55910,7 +55910,7 @@
         <v>45219</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         <v>45219</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56024,7 +56024,7 @@
         <v>45219</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56081,7 +56081,7 @@
         <v>45222</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45222</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45223</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>45223</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45224</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>45225</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45226</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45226</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56537,7 +56537,7 @@
         <v>45226</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>45229</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56651,7 +56651,7 @@
         <v>45229</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -56708,7 +56708,7 @@
         <v>45229</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -56770,7 +56770,7 @@
         <v>45229</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>45229</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45229</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -56946,7 +56946,7 @@
         <v>45229</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45230</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57065,7 +57065,7 @@
         <v>45232</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>45232</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57179,7 +57179,7 @@
         <v>45232</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45232</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57293,7 +57293,7 @@
         <v>45232</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45232</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57407,7 +57407,7 @@
         <v>45232</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57464,7 +57464,7 @@
         <v>45232</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57521,7 +57521,7 @@
         <v>45235</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>45235</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>45238</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>45240</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -57749,7 +57749,7 @@
         <v>45240</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -57863,7 +57863,7 @@
         <v>45245</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -57920,7 +57920,7 @@
         <v>45245</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -57977,7 +57977,7 @@
         <v>45245</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58034,7 +58034,7 @@
         <v>45245</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45245</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58148,7 +58148,7 @@
         <v>45245</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>45246</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58262,7 +58262,7 @@
         <v>45246</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58319,7 +58319,7 @@
         <v>45246</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>45246</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58433,7 +58433,7 @@
         <v>45247</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58490,7 +58490,7 @@
         <v>45247</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58547,7 +58547,7 @@
         <v>45250</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>45250</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>45250</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>45253</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45253</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>45253</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45253</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -58946,7 +58946,7 @@
         <v>45254</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59003,7 +59003,7 @@
         <v>45257</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45257</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>45257</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59174,7 +59174,7 @@
         <v>45259</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59231,7 +59231,7 @@
         <v>45260</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>45260</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59345,7 +59345,7 @@
         <v>45260</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59402,7 +59402,7 @@
         <v>45260</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>45260</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59516,7 +59516,7 @@
         <v>45260</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59573,7 +59573,7 @@
         <v>45260</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59630,7 +59630,7 @@
         <v>45261</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         <v>45264</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         <v>45264</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -59801,7 +59801,7 @@
         <v>45265</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>45266</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>45266</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -59972,7 +59972,7 @@
         <v>45267</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>45267</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45267</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>45267</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60205,7 +60205,7 @@
         <v>45267</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>45267</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45271</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>45274</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60433,7 +60433,7 @@
         <v>45275</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>45275</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45279</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60614,7 +60614,7 @@
         <v>45279</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -60671,7 +60671,7 @@
         <v>45279</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45279</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -60785,7 +60785,7 @@
         <v>45279</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>45279</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -60899,7 +60899,7 @@
         <v>45279</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>45281</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61013,7 +61013,7 @@
         <v>45281</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61070,7 +61070,7 @@
         <v>45290</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45294</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61184,7 +61184,7 @@
         <v>45299</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61241,7 +61241,7 @@
         <v>45301</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61298,7 +61298,7 @@
         <v>45301</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61355,7 +61355,7 @@
         <v>45301</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45301</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45302</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>45302</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61583,7 +61583,7 @@
         <v>45303</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61640,7 +61640,7 @@
         <v>45307</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -61697,7 +61697,7 @@
         <v>45307</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45308</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45308</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45308</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>45308</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -61982,7 +61982,7 @@
         <v>45308</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62039,7 +62039,7 @@
         <v>45310</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62096,7 +62096,7 @@
         <v>45314</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62153,7 +62153,7 @@
         <v>45314</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62210,7 +62210,7 @@
         <v>45314</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62267,7 +62267,7 @@
         <v>45314</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62324,7 +62324,7 @@
         <v>45314</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62381,7 +62381,7 @@
         <v>45315</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62438,7 +62438,7 @@
         <v>45315</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62495,7 +62495,7 @@
         <v>45315</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>45315</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>45315</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -62666,7 +62666,7 @@
         <v>45315</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -62723,7 +62723,7 @@
         <v>45317</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -62780,7 +62780,7 @@
         <v>45317</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -62837,7 +62837,7 @@
         <v>45317</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -62894,7 +62894,7 @@
         <v>45320</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -62951,7 +62951,7 @@
         <v>45321</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63008,7 +63008,7 @@
         <v>45321</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63065,7 +63065,7 @@
         <v>45321</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>45321</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>45323</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>45324</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63293,7 +63293,7 @@
         <v>45327</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>45327</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63407,7 +63407,7 @@
         <v>45329</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63464,7 +63464,7 @@
         <v>45330</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63521,7 +63521,7 @@
         <v>45331</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63578,7 +63578,7 @@
         <v>45331</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
         <v>45333</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -63692,7 +63692,7 @@
         <v>45334</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -63749,7 +63749,7 @@
         <v>45334</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>45337</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>45337</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -63913,14 +63913,14 @@
     <row r="1073" ht="15" customHeight="1">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>A 6545-2024</t>
+          <t>A 6546-2024</t>
         </is>
       </c>
       <c r="B1073" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -63933,7 +63933,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -63970,14 +63970,14 @@
     <row r="1074" ht="15" customHeight="1">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>A 6546-2024</t>
+          <t>A 6545-2024</t>
         </is>
       </c>
       <c r="B1074" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -63990,7 +63990,7 @@
         </is>
       </c>
       <c r="G1074" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H1074" t="n">
         <v>0</v>
@@ -64034,7 +64034,7 @@
         <v>45341</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64091,7 +64091,7 @@
         <v>45348</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64148,7 +64148,7 @@
         <v>45348</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64205,7 +64205,7 @@
         <v>45348</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64262,7 +64262,7 @@
         <v>45348</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64324,7 +64324,7 @@
         <v>45349</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64386,7 +64386,7 @@
         <v>45351</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64443,7 +64443,7 @@
         <v>45351</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -64500,7 +64500,7 @@
         <v>45351</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -64550,14 +64550,14 @@
     <row r="1084" ht="15" customHeight="1">
       <c r="A1084" t="inlineStr">
         <is>
-          <t>A 8367-2024</t>
+          <t>A 8590-2024</t>
         </is>
       </c>
       <c r="B1084" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -64570,7 +64570,7 @@
         </is>
       </c>
       <c r="G1084" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H1084" t="n">
         <v>0</v>
@@ -64607,14 +64607,14 @@
     <row r="1085" ht="15" customHeight="1">
       <c r="A1085" t="inlineStr">
         <is>
-          <t>A 8590-2024</t>
+          <t>A 8367-2024</t>
         </is>
       </c>
       <c r="B1085" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -64627,7 +64627,7 @@
         </is>
       </c>
       <c r="G1085" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H1085" t="n">
         <v>0</v>
@@ -64671,7 +64671,7 @@
         <v>45352</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -64721,14 +64721,14 @@
     <row r="1087" ht="15" customHeight="1">
       <c r="A1087" t="inlineStr">
         <is>
-          <t>A 8501-2024</t>
+          <t>A 8505-2024</t>
         </is>
       </c>
       <c r="B1087" s="1" t="n">
         <v>45355</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -64746,7 +64746,7 @@
         </is>
       </c>
       <c r="G1087" t="n">
-        <v>10.3</v>
+        <v>0.6</v>
       </c>
       <c r="H1087" t="n">
         <v>0</v>
@@ -64783,14 +64783,14 @@
     <row r="1088" ht="15" customHeight="1">
       <c r="A1088" t="inlineStr">
         <is>
-          <t>A 8505-2024</t>
+          <t>A 8501-2024</t>
         </is>
       </c>
       <c r="B1088" s="1" t="n">
         <v>45355</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -64808,7 +64808,7 @@
         </is>
       </c>
       <c r="G1088" t="n">
-        <v>0.6</v>
+        <v>10.3</v>
       </c>
       <c r="H1088" t="n">
         <v>0</v>
@@ -64852,7 +64852,7 @@
         <v>45356</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>

--- a/Översikt KINDA.xlsx
+++ b/Översikt KINDA.xlsx
@@ -567,7 +567,7 @@
         <v>44826</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         <v>44872</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45474</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>45875</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>44939</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>45839.63804398148</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>44088</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>45154.71289351852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>44958</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>45726.67396990741</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>44340.79716435185</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>44743.39091435185</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>45813.49403935186</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45659.24403935186</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>45784.71938657408</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>45301</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>45235</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>45196</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45208</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         <v>45698.67474537037</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>45693.56063657408</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44754</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>44092</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>44690</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>44418</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>44706</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>45769.37408564815</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>44419</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>44642</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>44435</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>45317</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>44483</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45630.41168981481</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44886</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>44914.64768518518</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>44636</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         <v>45484</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>45796.54400462963</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>45625.60760416667</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45049</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>45517</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>44608.4999537037</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45841.6012962963</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>45680.41096064815</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45196.57292824074</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>45294</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>44090</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45484</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45861</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45875</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45834.58208333333</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44525</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44342</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>44258</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>45490.56811342593</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>44239</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>44805</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44076</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>44215</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>44463</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>44418</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44383.42700231481</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>44361.87231481481</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>44419</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44078</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44817.99954861111</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>44249</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44382</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>44852.60928240741</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44776</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>44687</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44218.77190972222</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44309</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44439</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44322</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>44873</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>44069.91276620371</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>44171</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44481</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>44484</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44308</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44743.54180555556</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44411</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>44284</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>44587</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>44729</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>44392</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>44416</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44483.77188657408</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>44568.4189699074</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>44113</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>44433</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44516.65936342593</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44799.57587962963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44782</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44171</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44447</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44739.56701388889</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44497</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44587</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44326</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44084</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44067</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44244</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44362</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44465</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44337</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>44337</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>44221</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44433</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44467.60280092592</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>44466.67244212963</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>44466.67746527777</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44313.64008101852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>44517.59907407407</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>44165</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44454.66991898148</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>44600</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         <v>44316</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44733.01248842593</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>44721.6180787037</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44364.44892361111</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44873.32138888889</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44739.55577546296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>44837</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>44077</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>44874</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44242</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>44714.53115740741</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>44697</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44734.56722222222</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>44805.56214120371</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>44704.65763888889</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44063</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>44466.67340277778</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44466.67462962963</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>44088</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>44451.97046296296</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>44733.02409722222</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44852</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>44603.75377314815</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44123</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44419</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>44836.74738425926</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>44454</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>44861</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>44483</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44839.62386574074</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44616.80707175926</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44445</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>44379</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44095</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>44484</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>44720</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44167</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>44357</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44789.39914351852</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44486</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>44796.31537037037</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44560</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45145.63927083334</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>44539.34103009259</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>44970.57682870371</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44123</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>45761.68296296296</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>44112</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45769.37105324074</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44069</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>45082.55885416667</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44991.5281712963</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45483.86824074074</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>45709.39152777778</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44799</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44799.57753472222</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45709.38978009259</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45684.57195601852</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44851.67681712963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>44068</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45188.64319444444</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45334.82431712963</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45160.3425</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44930.64962962963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44811.38229166667</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44319</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>45187</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45360.40449074074</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45360.41894675926</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>44725.33693287037</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44484</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44375</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45708.62505787037</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44907</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45349.48241898148</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45676</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         <v>45676.49690972222</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45775</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45035</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44897.60309027778</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>45049</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>45688.43620370371</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45775</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45379</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44266.44692129629</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45082.34861111111</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>45741.61278935185</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45266.61387731481</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44839.58741898148</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>45071</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44442.55604166666</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44160</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45400</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14384,7 +14384,7 @@
         <v>44379</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44982.5037962963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>45385</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>45699.45127314814</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45699.4584837963</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14679,7 +14679,7 @@
         <v>44732</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45148.70342592592</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>45315.66575231482</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45226.62546296296</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>44284.57011574074</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45461.42116898148</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>45758.36638888889</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         <v>45400.7590162037</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45737.5596875</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>45757.48918981481</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45315.66914351852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45321.70762731481</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45315.66689814815</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>44868</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15482,7 +15482,7 @@
         <v>45078.5274537037</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>45442.48741898148</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>45562.3316087963</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45360.4172337963</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>44958.38997685185</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>44755.45060185185</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45539.66679398148</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45259.31565972222</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44323</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>45307.48108796297</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44977</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>45314.33872685185</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45757.48659722223</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45468.49909722222</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45758.36324074074</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45551.28467592593</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>44952.00760416667</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45219</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45201.40716435185</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>45708.46913194445</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45708.46960648148</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>45517.44506944445</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>44956</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>44483.65453703704</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>44517</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45576.67208333333</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45240.34232638889</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44452</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>44959.3233912037</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>44952</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>45048</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>45162</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>44918.3396875</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45008</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>44868</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45544.6372337963</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45572.6625</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>44266</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45631.62002314815</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45001.72512731481</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45294.43197916666</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>44965.67148148148</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>44120</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45086.66693287037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>44112</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45671.62480324074</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45733.66236111111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45660.71824074074</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45393</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45485.4796875</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45770.65983796296</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45476.34908564815</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45120</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>45770.67305555556</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45161</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45161.36759259259</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>45161.36928240741</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18833,7 +18833,7 @@
         <v>45601.3566087963</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18895,7 +18895,7 @@
         <v>45601.35923611111</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>45341</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45331</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>44923.40631944445</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45475.62894675926</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45145</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19247,7 +19247,7 @@
         <v>45776.47818287037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45096</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>45776.44575231482</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>45776.48627314815</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19475,7 +19475,7 @@
         <v>45777.55960648148</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45195</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45327.4684375</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45761</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>45777.47508101852</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45777.48113425926</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>44084</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>45614.39091435185</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45082</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45560.2703125</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45784.59287037037</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45784.70443287037</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45593.32488425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45448.52539351852</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>44575</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45699.45978009259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45456.44684027778</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>45475</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         <v>45361.75074074074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45785.24804398148</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>44918.32740740741</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44918.33414351852</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>44918</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45348.6147337963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45531.64934027778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>44988</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45539.46399305556</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44650.56546296296</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45476.57782407408</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>44567.77518518519</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>45358.44520833333</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45786</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45786.62056712963</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>44952</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45527.33670138889</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45527.3469212963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45267.61618055555</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45250</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45517.61326388889</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45007.45686342593</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45456.61288194444</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45020.71773148148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45390.53634259259</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>44953</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45755.59559027778</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45260.80365740741</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45786</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22189,7 +22189,7 @@
         <v>45302.51340277777</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45755.59457175926</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>45632.59153935185</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>45785.34126157407</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22417,7 +22417,7 @@
         <v>45355.45898148148</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45789.67461805556</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22536,7 +22536,7 @@
         <v>45750.62378472222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>45786</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45671.62322916667</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45014.65841435185</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>45123.60599537037</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>45383</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>45601.36060185185</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45533.54908564815</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>44454.66972222222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>45470.88379629629</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45526</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45098.70277777778</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45484</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45139</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>45369.62628472222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45789.67196759259</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>45567.47780092592</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45333.84959490741</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23567,7 +23567,7 @@
         <v>45351</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>44462</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>44207</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45145</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45719.49922453704</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45792.37238425926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>44657</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44148.37969907407</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45754.46814814815</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24110,7 +24110,7 @@
         <v>45576.65969907407</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45791</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45442.6459837963</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>45601.35335648148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>45188.66209490741</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>45000.65476851852</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44594</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45071</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45560.64243055556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>44974.57886574074</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>45796.63424768519</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44964</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>45160</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>45838.72785879629</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>45613.8235300926</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>45229</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45588.49065972222</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45635.68952546296</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45187</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45835.35780092593</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45796.63584490741</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45796.54888888889</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>45835.36383101852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45624</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45141</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44918.34784722222</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45698.67719907407</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45235</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45595.59052083334</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>45796.63180555555</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         <v>45540.59917824074</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45007</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45839.57368055556</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>45798.33824074074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45798.33460648148</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45078.52990740741</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45078</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>45160.34069444444</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45684.49472222223</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>45839.51413194444</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44701</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>44795</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26524,7 +26524,7 @@
         <v>44677</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>45839.50966435186</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>45385.56655092593</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45746.48921296297</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45840.85745370371</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45062</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26866,7 +26866,7 @@
         <v>45839.58341435185</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>44608.48450231482</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45324.44579861111</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>44144</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45062.57160879629</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45755.61784722222</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45841.49861111111</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>45799</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27327,7 +27327,7 @@
         <v>45799.36881944445</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27384,7 +27384,7 @@
         <v>44266</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>44203</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45841.4630787037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>45841.50858796296</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
